--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Carlito"/>
       <sz val="11"/>
@@ -107,8 +107,16 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -136,6 +144,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -150,7 +163,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -224,6 +237,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2167,7 +2189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="60.58203125" customWidth="1" min="1" max="4"/>
@@ -3104,6 +3126,204 @@
           <t>문구세트 단계(입문 → 기본) · 적용 메모</t>
         </is>
       </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>연구소 반영본(diet-1.1.0.json) 대비 바꿀 것 · 2026-10-19</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="n"/>
+      <c r="C60" s="30" t="n"/>
+      <c r="D60" s="30" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>diet-1.1.0.json과 비교한 결과. 끼니별 식사 시각 단계는 넣지 않는다. 문구별 목록은 데이터계약 파일의 「1.1.0 대비 변경」 시트.</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="n"/>
+      <c r="C61" s="30" t="n"/>
+      <c r="D61" s="30" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="n"/>
+      <c r="B62" s="30" t="n"/>
+      <c r="C62" s="30" t="n"/>
+      <c r="D62" s="30" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>지금(1.1.0)</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>바꿀 것</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="inlineStr">
+        <is>
+          <t>JSON 위치 · 이 파일 시트</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>고정 질문 선택지 글자</t>
+        </is>
+      </c>
+      <c r="B64" s="30" t="inlineStr">
+        <is>
+          <t>평소대로 / 조금 적게 / 거의 못 먹음 (As usual / A bit less / Barely ate)</t>
+        </is>
+      </c>
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>충분히 먹음 / 적게 · 몇 입만 / 못 먹거나 거름 (Ate enough / Less, a few bites / Didn't eat or skipped). 코드 · 점수 · 순서는 그대로</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
+        <is>
+          <t>options question_key_1 · 선택지 DIET-Q-00 · 번역_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="30" t="inlineStr">
+        <is>
+          <t>목표 문구 타일 글자</t>
+        </is>
+      </c>
+      <c r="B65" s="30" t="inlineStr">
+        <is>
+          <t>특정 음식·혼자/가족/도시락 전제가 든 문구 61개</t>
+        </is>
+      </c>
+      <c r="C65" s="30" t="inlineStr">
+        <is>
+          <t>음식 종류로 넓힌 문구로 교체(예: 라면 국물은 남기기 → 국물 음식은 국물 남기기). 영어 61개도 함께</t>
+        </is>
+      </c>
+      <c r="D65" s="30" t="inlineStr">
+        <is>
+          <t>goal_phrases tile_text_ko · tile_text_en · 목표문구 tile_text · 번역_en</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="30" t="inlineStr">
+        <is>
+          <t>목표 문구 단계</t>
+        </is>
+      </c>
+      <c r="B66" s="30" t="inlineStr">
+        <is>
+          <t>입문(INTRO)인 「A 대신 B」 문구 20개</t>
+        </is>
+      </c>
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>기본(BASE)으로 옮김. 「야식 대신 물 한 잔 · 따뜻한 차」는 입문 유지</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
+        <is>
+          <t>goal_phrases stage_code · 목표문구 stage_code</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>이유 한 줄</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>39개가 옛 문장</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>바뀐 타일에 맞춘 문장으로 교체(화면 미노출)</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>goal_phrases reason_text_ko · 목표문구 reason_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>풀어 쓴 문구</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>title_text_full_context_ko가 403개 모두 비어 있음</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>목표문구 full_text 값을 채움(40자 이내 한 문장). 영어는 번역 뒤</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>goal_phrases title_text_full_context_ko · 목표문구 full_text</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>목표 단계 오르기 기준</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>stage_up_window_days 7 · stage_up_completions 3 (7일 안 3번 완료)</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>최근 목표 4개 중 완료 3개 · 끝난 목표 3개 이상이면 한 칸 오름, 56일보다 오래된 목표는 세지 않음. 「관찰 중」 축만 오르고 「개선 필요」 축은 기본까지</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>policy · 설정파라미터 CFG-010 · CFG-068 · CFG-069 · CFG-071</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>그대로인 것</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>질문 9개 문장 · 회전 선택지 · 질환규칙 14 · 연결축 15 · 금지성격 28 · 상병코드 61 · 내정보질환 4 · 검진 연결 4 · 판정그룹 15 · 달력 13</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>바꿀 것 없음</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA069ED-3740-4DC0-9CD6-111D13F58FFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E1DCFF5-AFDF-44F6-B4DB-7AE31C97B2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="42240" yWindow="2460" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9935,7 +9935,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10016,6 +10016,24 @@
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -10064,7 +10082,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10141,6 +10159,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12687,16 +12717,16 @@
       </c>
     </row>
     <row r="59" spans="1:4" ht="52">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="32" t="s">
         <v>3286</v>
       </c>
-      <c r="B59" s="26" t="s">
+      <c r="B59" s="32" t="s">
         <v>3287</v>
       </c>
-      <c r="C59" s="26" t="s">
+      <c r="C59" s="32" t="s">
         <v>3288</v>
       </c>
-      <c r="D59" s="26" t="s">
+      <c r="D59" s="32" t="s">
         <v>3289</v>
       </c>
     </row>
@@ -12821,16 +12851,16 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="28">
-      <c r="A71" s="28" t="s">
+      <c r="A71" s="33" t="s">
         <v>3290</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="33" t="s">
         <v>3291</v>
       </c>
-      <c r="C71" s="28" t="s">
+      <c r="C71" s="33" t="s">
         <v>3292</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="D71" s="33" t="s">
         <v>3293</v>
       </c>
     </row>
@@ -44968,7 +44998,7 @@
         <v>3144</v>
       </c>
       <c r="H370" s="8">
-        <f t="shared" ref="H370:H433" si="3">LEN(G370)</f>
+        <f t="shared" ref="H370:H404" si="3">LEN(G370)</f>
         <v>12</v>
       </c>
       <c r="I370" s="4" t="s">
@@ -47854,7 +47884,7 @@
       <c r="C23" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="31">
         <v>365</v>
       </c>
       <c r="E23" s="4"/>
@@ -47864,7 +47894,7 @@
       <c r="G23" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="31" t="s">
         <v>3285</v>
       </c>
     </row>
@@ -49551,13 +49581,13 @@
       <c r="C64" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="30" t="s">
         <v>3283</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="F64" s="30" t="s">
         <v>3284</v>
       </c>
     </row>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5F83B49-4052-4F5B-B115-BDD1FDF4747C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D137846-0D9F-4C1F-BD32-FC01074D7051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="2660" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -12085,640 +12085,640 @@
     <col min="5" max="5" width="10.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:4" ht="15.5">
+      <c r="A1" s="33" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="56">
+      <c r="A2" s="32" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>3262</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="42">
+      <c r="A5" s="32" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>3265</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="42">
+      <c r="A6" s="32" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>3269</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28">
+      <c r="A7" s="32" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>3274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="42">
+      <c r="A8" s="32" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>3276</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>3277</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28">
+      <c r="A9" s="32" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>3280</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>3281</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28">
+      <c r="A10" s="32" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>3284</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>3285</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>3286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="42">
+      <c r="A11" s="32" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>3290</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>3291</v>
+      </c>
+      <c r="D11" s="32"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B13" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C13" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="15" t="str">
-        <f>COUNTA(문구세트!A2:A999)&amp;"개 운영 문구 · 문구 ID · 성격"</f>
-        <v>403개 운영 문구 · 문구 ID · 성격</v>
-      </c>
-      <c r="C5" s="15">
-        <f>COUNTA(문구세트!A2:A999)</f>
-        <v>403</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
-        <v>8</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="3">
-        <v>61</v>
-      </c>
-      <c r="D8" s="4"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3">
-        <v>62</v>
-      </c>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3">
-        <v>63</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="15" t="str">
-        <f>"문구 "&amp;COUNTA(노출조건!A2:A999)&amp;"개의 시간·요일·상황 분리와 자동 적용 여부"</f>
-        <v>문구 403개의 시간·요일·상황 분리와 자동 적용 여부</v>
-      </c>
-      <c r="C11" s="15">
-        <f>COUNTA(노출조건!A2:A999)</f>
-        <v>403</v>
-      </c>
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="3">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="3">
-        <v>4</v>
-      </c>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" ht="25" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="3">
-        <v>4</v>
-      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
       <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="15" t="str">
+        <f>COUNTA(문구세트!A2:A999)&amp;"개 운영 문구 · 문구 ID · 성격"</f>
+        <v>403개 운영 문구 · 문구 ID · 성격</v>
+      </c>
+      <c r="C17" s="15">
+        <f>COUNTA(문구세트!A2:A999)</f>
+        <v>403</v>
+      </c>
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3">
+        <v>8</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="3">
+        <v>14</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="3">
+        <v>61</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3">
+        <v>62</v>
+      </c>
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="3">
+        <v>63</v>
+      </c>
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="15" t="str">
+        <f>"문구 "&amp;COUNTA(노출조건!A2:A999)&amp;"개의 시간·요일·상황 분리와 자동 적용 여부"</f>
+        <v>문구 403개의 시간·요일·상황 분리와 자동 적용 여부</v>
+      </c>
+      <c r="C23" s="15">
+        <f>COUNTA(노출조건!A2:A999)</f>
+        <v>403</v>
+      </c>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="3">
+        <v>20</v>
+      </c>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="3">
+        <v>4</v>
+      </c>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="1:4" ht="25" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="3">
+        <v>4</v>
+      </c>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C29" s="15" t="str">
         <f>"1 ~ 225 (현재 "&amp;COUNTA(문구세트!A2:A999)&amp;"개)"</f>
         <v>1 ~ 225 (현재 403개)</v>
       </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="25" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="3">
-        <v>10</v>
-      </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:4" ht="25" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26" spans="1:4" ht="25" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27" spans="1:4" ht="25" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28" spans="1:4" ht="25" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="D29" s="4"/>
     </row>
     <row r="30" spans="1:4" ht="25" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" s="3"/>
+        <v>32</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="D30" s="4"/>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>36</v>
+      </c>
       <c r="D31" s="4"/>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="D32" s="4"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="3" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D33" s="4"/>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="3" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D34" s="4"/>
     </row>
-    <row r="35" spans="1:4" ht="25" customHeight="1">
+    <row r="35" spans="1:4">
       <c r="A35" s="3" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>72</v>
+        <v>47</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="D35" s="4"/>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="3" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>74</v>
+        <v>50</v>
+      </c>
+      <c r="C36" s="3">
+        <v>10</v>
       </c>
       <c r="D36" s="4"/>
     </row>
     <row r="37" spans="1:4" ht="25" customHeight="1">
       <c r="A37" s="3" t="s">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="D37" s="4"/>
     </row>
     <row r="38" spans="1:4" ht="25" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D38" s="4"/>
     </row>
     <row r="39" spans="1:4" ht="25" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="D39" s="4"/>
     </row>
     <row r="40" spans="1:4" ht="25" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="D40" s="4"/>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="3" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C41" s="3">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>65</v>
       </c>
       <c r="D41" s="4"/>
     </row>
     <row r="42" spans="1:4" ht="25" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="4"/>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>86</v>
-      </c>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="4"/>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
+      <c r="A44" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
       <c r="D44" s="4"/>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
+      <c r="A45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="D45" s="4"/>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
+      <c r="A46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="D46" s="4"/>
     </row>
-    <row r="47" spans="1:4" ht="15.5">
-      <c r="A47" s="33" t="s">
-        <v>3261</v>
-      </c>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-    </row>
-    <row r="48" spans="1:4" ht="56">
-      <c r="A48" s="32" t="s">
-        <v>3288</v>
-      </c>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" s="28" t="s">
-        <v>88</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>3262</v>
-      </c>
-      <c r="C50" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D50" s="28" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="42">
-      <c r="A51" s="32" t="s">
-        <v>3263</v>
-      </c>
-      <c r="B51" s="32" t="s">
-        <v>3264</v>
-      </c>
-      <c r="C51" s="32" t="s">
-        <v>3265</v>
-      </c>
-      <c r="D51" s="32" t="s">
-        <v>3266</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="42">
-      <c r="A52" s="32" t="s">
-        <v>3267</v>
-      </c>
-      <c r="B52" s="32" t="s">
-        <v>3268</v>
-      </c>
-      <c r="C52" s="32" t="s">
-        <v>3269</v>
-      </c>
-      <c r="D52" s="32" t="s">
-        <v>3270</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28">
-      <c r="A53" s="32" t="s">
-        <v>3271</v>
-      </c>
-      <c r="B53" s="32" t="s">
-        <v>3272</v>
-      </c>
-      <c r="C53" s="32" t="s">
-        <v>3273</v>
-      </c>
-      <c r="D53" s="32" t="s">
-        <v>3274</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="42">
-      <c r="A54" s="32" t="s">
-        <v>3275</v>
-      </c>
-      <c r="B54" s="32" t="s">
-        <v>3276</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>3277</v>
-      </c>
-      <c r="D54" s="32" t="s">
-        <v>3278</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="28">
-      <c r="A55" s="32" t="s">
-        <v>3279</v>
-      </c>
-      <c r="B55" s="32" t="s">
-        <v>3280</v>
-      </c>
-      <c r="C55" s="32" t="s">
-        <v>3281</v>
-      </c>
-      <c r="D55" s="32" t="s">
-        <v>3282</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="28">
-      <c r="A56" s="32" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B56" s="32" t="s">
-        <v>3284</v>
-      </c>
-      <c r="C56" s="32" t="s">
-        <v>3285</v>
-      </c>
-      <c r="D56" s="32" t="s">
-        <v>3286</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="42">
-      <c r="A57" s="32" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B57" s="32" t="s">
-        <v>3290</v>
-      </c>
-      <c r="C57" s="32" t="s">
-        <v>3291</v>
-      </c>
-      <c r="D57" s="32"/>
+    <row r="47" spans="1:4" ht="25" customHeight="1">
+      <c r="A47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="1:4" ht="25" customHeight="1">
+      <c r="A49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D49" s="4"/>
+    </row>
+    <row r="50" spans="1:4" ht="25" customHeight="1">
+      <c r="A50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D50" s="4"/>
+    </row>
+    <row r="51" spans="1:4" ht="25" customHeight="1">
+      <c r="A51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D51" s="4"/>
+    </row>
+    <row r="52" spans="1:4" ht="25" customHeight="1">
+      <c r="A52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D52" s="4"/>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="3">
+        <v>62</v>
+      </c>
+      <c r="D53" s="4"/>
+    </row>
+    <row r="54" spans="1:4" ht="25" customHeight="1">
+      <c r="A54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C54" s="3"/>
+      <c r="D54" s="4"/>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C55" s="3"/>
+      <c r="D55" s="4"/>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D137846-0D9F-4C1F-BD32-FC01074D7051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAA35C4C-223F-4321-8007-69E63A655859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10662" uniqueCount="3292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10680" uniqueCount="3297">
   <si>
     <t>maiReport 식이 참조·설정 데이터 · v1.4.0 · 연구소 전달본(끼니별 식사 시각 단계 제외)</t>
   </si>
@@ -9936,14 +9936,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. 끼니별 식사 시각 단계(v1.3.0)는 다음 버전에 넣으므로 이 전달본에서 뺐다. · 최근 것이 위</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 콘솔 1.1.1 내보내기(현재 적용 중)를 이 파일과 비교한 결과. 질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 모두 같고, 아래 표의 항목만 다름. 값 단위 목록은 데이터계약 파일 「1.1.1 대비 변경」 시트. 항목 앞 [꼭 수정] · [권장] · [확인] · [참고]가 할 일의 정도.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>[그대로] 나머지</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -9953,6 +9945,93 @@
   </si>
   <si>
     <t>바꿀 것 없음</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>상태</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>변경</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>확인</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7F6000"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>필요</t>
+    </r>
+  </si>
+  <si>
+    <t>참고</t>
+  </si>
+  <si>
+    <r>
+      <t>반영</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF375623"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>완료</t>
+    </r>
+  </si>
+  <si>
+    <t>v1.1.0 · v1.2.0 · v1.3.0 · v1.4.0에서 바꾼 것. 파일 이름은 v1.0.0 그대로 둔다. 끼니별 식사 시각 단계(v1.3.0)는 다음 버전에 넣으므로 이 전달본에서 뺐다. · 최근 것이 위 · 반영 완료 8건은 맨 아래에 숨김(행 번호 사이를 우클릭 → 숨기기 취소)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리자 콘솔 1.1.1 내보내기(현재 적용 중)를 이 파일과 비교한 결과. 질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 모두 같고, 아래 표의 항목만 다름. 바꿀 값은 표의 「바꿀 것」 칸에 적음. 항목 앞 [꼭 수정] · [권장] · [확인] · [참고]가 할 일의 정도. · 반영 완료 1건은 맨 아래에 숨김(행 번호 사이를 우클릭 → 숨기기 취소)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -9960,7 +10039,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10060,8 +10139,53 @@
       <color rgb="FFFF0000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7F6000"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF375623"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10094,6 +10218,30 @@
         <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE0E0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -10108,7 +10256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10198,6 +10346,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12078,14 +12238,14 @@
   <sheetPr>
     <tabColor rgb="FF315A7D"/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="60.58203125" customWidth="1"/>
-    <col min="5" max="5" width="10.58203125" customWidth="1"/>
+    <col min="5" max="5" width="11.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.5">
+    <row r="1" spans="1:5" ht="15.5">
       <c r="A1" s="33" t="s">
         <v>3261</v>
       </c>
@@ -12093,15 +12253,15 @@
       <c r="C1" s="27"/>
       <c r="D1" s="27"/>
     </row>
-    <row r="2" spans="1:4" ht="56">
+    <row r="2" spans="1:5" ht="70">
       <c r="A2" s="32" t="s">
-        <v>3288</v>
+        <v>3296</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="28" t="s">
         <v>88</v>
       </c>
@@ -12114,8 +12274,11 @@
       <c r="D4" s="28" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="42">
+      <c r="E4" s="28" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="42">
       <c r="A5" s="32" t="s">
         <v>3263</v>
       </c>
@@ -12128,8 +12291,11 @@
       <c r="D5" s="32" t="s">
         <v>3266</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="42">
+      <c r="E5" s="34" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="42">
       <c r="A6" s="32" t="s">
         <v>3267</v>
       </c>
@@ -12142,8 +12308,11 @@
       <c r="D6" s="32" t="s">
         <v>3270</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28">
+      <c r="E6" s="34" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28">
       <c r="A7" s="32" t="s">
         <v>3271</v>
       </c>
@@ -12156,8 +12325,11 @@
       <c r="D7" s="32" t="s">
         <v>3274</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="42">
+      <c r="E7" s="35" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="42">
       <c r="A8" s="32" t="s">
         <v>3275</v>
       </c>
@@ -12170,8 +12342,11 @@
       <c r="D8" s="32" t="s">
         <v>3278</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="28">
+      <c r="E8" s="35" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28">
       <c r="A9" s="32" t="s">
         <v>3279</v>
       </c>
@@ -12184,8 +12359,11 @@
       <c r="D9" s="32" t="s">
         <v>3282</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="28">
+      <c r="E9" s="35" t="s">
+        <v>3292</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28">
       <c r="A10" s="32" t="s">
         <v>3283</v>
       </c>
@@ -12198,20 +12376,26 @@
       <c r="D10" s="32" t="s">
         <v>3286</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="42">
+      <c r="E10" s="36" t="s">
+        <v>3293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="42" hidden="1">
       <c r="A11" s="32" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C11" s="32" t="s">
         <v>3289</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>3290</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>3291</v>
-      </c>
       <c r="D11" s="32"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E11" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" s="23" t="s">
         <v>0</v>
       </c>
@@ -12223,7 +12407,7 @@
       </c>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="37.5" customHeight="1">
+    <row r="14" spans="1:5" ht="37.5" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>3</v>
       </c>
@@ -12231,13 +12415,13 @@
       <c r="C14" s="3"/>
       <c r="D14" s="4"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:5">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
@@ -12622,7 +12806,7 @@
       </c>
       <c r="D48" s="4"/>
     </row>
-    <row r="49" spans="1:4" ht="25" customHeight="1">
+    <row r="49" spans="1:5" ht="25" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>10</v>
       </c>
@@ -12634,7 +12818,7 @@
       </c>
       <c r="D49" s="4"/>
     </row>
-    <row r="50" spans="1:4" ht="25" customHeight="1">
+    <row r="50" spans="1:5" ht="25" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>12</v>
       </c>
@@ -12646,7 +12830,7 @@
       </c>
       <c r="D50" s="4"/>
     </row>
-    <row r="51" spans="1:4" ht="25" customHeight="1">
+    <row r="51" spans="1:5" ht="25" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>10</v>
       </c>
@@ -12658,7 +12842,7 @@
       </c>
       <c r="D51" s="4"/>
     </row>
-    <row r="52" spans="1:4" ht="25" customHeight="1">
+    <row r="52" spans="1:5" ht="25" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>10</v>
       </c>
@@ -12670,7 +12854,7 @@
       </c>
       <c r="D52" s="4"/>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
         <v>14</v>
       </c>
@@ -12682,7 +12866,7 @@
       </c>
       <c r="D53" s="4"/>
     </row>
-    <row r="54" spans="1:4" ht="25" customHeight="1">
+    <row r="54" spans="1:5" ht="25" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>83</v>
       </c>
@@ -12692,7 +12876,7 @@
       <c r="C54" s="3"/>
       <c r="D54" s="4"/>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
         <v>85</v>
       </c>
@@ -12702,25 +12886,25 @@
       <c r="C55" s="3"/>
       <c r="D55" s="4"/>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:5">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:5">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:5">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:5">
       <c r="A59" s="4" t="s">
         <v>87</v>
       </c>
@@ -12728,15 +12912,15 @@
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
     </row>
-    <row r="60" spans="1:4" ht="37.5">
+    <row r="60" spans="1:5" ht="37.5">
       <c r="A60" s="4" t="s">
-        <v>3287</v>
+        <v>3295</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:5">
       <c r="A62" s="4" t="s">
         <v>88</v>
       </c>
@@ -12749,8 +12933,11 @@
       <c r="D62" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="52">
+      <c r="E62" s="4" t="s">
+        <v>3290</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="52">
       <c r="A63" s="31" t="s">
         <v>3257</v>
       </c>
@@ -12763,8 +12950,11 @@
       <c r="D63" s="31" t="s">
         <v>3260</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="52">
+      <c r="E63" s="34" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="52" hidden="1">
       <c r="A64" s="26" t="s">
         <v>118</v>
       </c>
@@ -12777,8 +12967,11 @@
       <c r="D64" s="26" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" ht="65">
+      <c r="E64" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="65" hidden="1">
       <c r="A65" s="26" t="s">
         <v>115</v>
       </c>
@@ -12791,8 +12984,11 @@
       <c r="D65" s="26" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" ht="39">
+      <c r="E65" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="39" hidden="1">
       <c r="A66" s="26" t="s">
         <v>112</v>
       </c>
@@ -12805,8 +13001,11 @@
       <c r="D66" s="26" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" ht="78">
+      <c r="E66" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="78" hidden="1">
       <c r="A67" s="26" t="s">
         <v>108</v>
       </c>
@@ -12819,8 +13018,11 @@
       <c r="D67" s="26" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="39" customHeight="1">
+      <c r="E67" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A68" s="26" t="s">
         <v>104</v>
       </c>
@@ -12833,8 +13035,11 @@
       <c r="D68" s="26" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="39" customHeight="1">
+      <c r="E68" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A69" s="26" t="s">
         <v>100</v>
       </c>
@@ -12847,8 +13052,11 @@
       <c r="D69" s="26" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="39" customHeight="1">
+      <c r="E69" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="39" hidden="1" customHeight="1">
       <c r="A70" s="26" t="s">
         <v>96</v>
       </c>
@@ -12861,8 +13069,11 @@
       <c r="D70" s="26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="37" t="s">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" hidden="1">
       <c r="A71" s="26" t="s">
         <v>92</v>
       </c>
@@ -12874,6 +13085,9 @@
       </c>
       <c r="D71" s="26" t="s">
         <v>95</v>
+      </c>
+      <c r="E71" s="37" t="s">
+        <v>3294</v>
       </c>
     </row>
   </sheetData>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB59FB8-8004-481D-A1F7-370F25D0F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9E4A0F-D0F2-495C-8A3E-D322146F1317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="먼저 읽기" sheetId="13" r:id="rId1"/>
+    <sheet name="안내" sheetId="13" r:id="rId1"/>
     <sheet name="축정의" sheetId="2" r:id="rId2"/>
     <sheet name="설정파라미터" sheetId="3" r:id="rId3"/>
     <sheet name="설정값" sheetId="4" r:id="rId4"/>
@@ -9800,323 +9800,6 @@
   </si>
   <si>
     <t>참고</t>
-  </si>
-  <si>
-    <r>
-      <t>식이</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>참조</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>·</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>설정</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>먼저</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>읽기</t>
-    </r>
-  </si>
-  <si>
-    <t>이 시트만 보면 됩니다. 읽는 순서는 ① 지금 연구소가 할 일 → ② 이 파일 기본 정보 → ③ 이 파일에서 바뀐 내용입니다. 맨 앞 「상태」 칸의 색 배지로 할 일을 구분합니다. 「반영 완료」 줄은 숨겨 두었습니다(행 번호 사이를 우클릭 → 숨기기 취소).</t>
-  </si>
-  <si>
-    <r>
-      <t>①</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>지금</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>연구소가</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>할</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>일</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>관리자</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>콘솔</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> diet-1.1.1(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>현재</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>적용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>중</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>과</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>비교</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF1F4E79"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> · 2026-10-19</t>
-    </r>
   </si>
   <si>
     <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「꼭 수정」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
@@ -10863,6 +10546,18 @@
       </rPr>
       <t>필요</t>
     </r>
+  </si>
+  <si>
+    <t>식이 참조·설정 데이터 · 안내</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 시트만 보면 됩니다. 읽는 순서는 ① 연구소 전달용 → ② 이 파일 기본 정보 → ③ 이 파일에서 바뀐 내용입니다. 맨 앞 「상태」 칸의 색 배지로 할 일을 구분합니다. 「반영 완료」 줄은 숨겨 두었습니다(행 번호 사이를 우클릭 → 숨기기 취소).</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>① 연구소 전달용 · 관리자 콘솔 diet-1.1.1(현재 적용 중)과 비교 · 2026-10-19</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -11219,31 +10914,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11261,13 +10941,19 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11276,8 +10962,17 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13170,866 +12865,908 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="44" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+    </row>
+    <row r="2" spans="1:5" ht="34" customHeight="1">
+      <c r="A2" s="38" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="36" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1">
+      <c r="A5" s="38" t="s">
         <v>3251</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-    </row>
-    <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="28" t="s">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+    </row>
+    <row r="6" spans="1:5" ht="20" customHeight="1">
+      <c r="A6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="26" t="s">
         <v>3252</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>3253</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-    </row>
-    <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="28" t="s">
+      <c r="D6" s="26" t="s">
         <v>3254</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-    </row>
-    <row r="6" spans="1:5" ht="20" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="E6" s="26" t="s">
+        <v>3255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="48" customHeight="1">
+      <c r="A7" s="29" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>3257</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>3258</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="48" customHeight="1">
+      <c r="A8" s="31" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>3262</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>3263</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="48" customHeight="1">
+      <c r="A9" s="32" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>3266</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>3267</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>3268</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>3269</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="48" customHeight="1">
+      <c r="A10" s="32" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>3274</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="33" customHeight="1">
+      <c r="A11" s="32" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>3275</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>3276</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>3278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="48" customHeight="1">
+      <c r="A12" s="33" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>3279</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>3280</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>3281</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>3282</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A13" s="34" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>3284</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>3285</v>
+      </c>
+      <c r="E13" s="28"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="36" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+    </row>
+    <row r="16" spans="1:5" ht="20" customHeight="1">
+      <c r="B16" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+    </row>
+    <row r="17" spans="2:5" ht="18" customHeight="1">
+      <c r="B17" s="27" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>3289</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+    </row>
+    <row r="18" spans="2:5" ht="33" customHeight="1">
+      <c r="B18" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="C18" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+    </row>
+    <row r="19" spans="2:5" ht="18" customHeight="1">
+      <c r="B19" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+    </row>
+    <row r="20" spans="2:5" ht="18" customHeight="1">
+      <c r="B20" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+    </row>
+    <row r="22" spans="2:5" ht="20" customHeight="1">
+      <c r="B22" s="41" t="s">
+        <v>3290</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+    </row>
+    <row r="23" spans="2:5" ht="20" customHeight="1">
+      <c r="B23" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="42"/>
+      <c r="E23" s="26" t="s">
+        <v>3291</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="18" customHeight="1">
+      <c r="B24" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>3292</v>
+      </c>
+      <c r="D24" s="43"/>
+      <c r="E24" s="27">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" ht="18" customHeight="1">
+      <c r="B25" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="39"/>
+      <c r="E25" s="30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" ht="18" customHeight="1">
+      <c r="B26" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="39"/>
+      <c r="E26" s="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" ht="18" customHeight="1">
+      <c r="B27" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="39"/>
+      <c r="E27" s="30">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="18" customHeight="1">
+      <c r="B28" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="39"/>
+      <c r="E28" s="30">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="18" customHeight="1">
+      <c r="B29" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" s="39"/>
+      <c r="E29" s="30">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" ht="18" customHeight="1">
+      <c r="B30" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>3293</v>
+      </c>
+      <c r="D30" s="39"/>
+      <c r="E30" s="30">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="18" customHeight="1">
+      <c r="B31" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="39"/>
+      <c r="E31" s="30">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="18" customHeight="1">
+      <c r="B32" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="39"/>
+      <c r="E32" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="33" customHeight="1">
+      <c r="B33" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="40"/>
+      <c r="E33" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="20" customHeight="1">
+      <c r="B35" s="41" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
+    </row>
+    <row r="36" spans="2:5" ht="20" customHeight="1">
+      <c r="B36" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="D36" s="42"/>
+      <c r="E36" s="26" t="s">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="18" customHeight="1">
+      <c r="B37" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="43"/>
+      <c r="E37" s="27" t="s">
+        <v>3296</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" ht="18" customHeight="1">
+      <c r="B38" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D38" s="39"/>
+      <c r="E38" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" ht="18" customHeight="1">
+      <c r="B39" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="31" t="s">
-        <v>3255</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>3256</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>3257</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>3258</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="48" customHeight="1">
-      <c r="A7" s="34" t="s">
-        <v>3263</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>3259</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>3260</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>3261</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>3262</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="48" customHeight="1">
-      <c r="A8" s="36" t="s">
-        <v>3268</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>3264</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>3265</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>3266</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>3267</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="48" customHeight="1">
-      <c r="A9" s="37" t="s">
-        <v>3273</v>
-      </c>
-      <c r="B9" s="35" t="s">
-        <v>3269</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>3270</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>3271</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>3272</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="37" t="s">
-        <v>3273</v>
-      </c>
-      <c r="B10" s="35" t="s">
-        <v>3274</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>3275</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>3276</v>
-      </c>
-      <c r="E10" s="35" t="s">
-        <v>3277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="37" t="s">
-        <v>3273</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>3278</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>3279</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>3280</v>
-      </c>
-      <c r="E11" s="35" t="s">
-        <v>3281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="48" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>3250</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>3282</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>3283</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>3284</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>3285</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A13" s="39" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B13" s="33" t="s">
+      <c r="C39" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="33" customHeight="1">
+      <c r="B40" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="39"/>
+      <c r="E40" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" ht="33" customHeight="1">
+      <c r="B41" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="39"/>
+      <c r="E41" s="30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="18" customHeight="1">
+      <c r="B42" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="39"/>
+      <c r="E42" s="30" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="18" customHeight="1">
+      <c r="B43" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D43" s="39"/>
+      <c r="E43" s="30" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="18" customHeight="1">
+      <c r="B44" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="39"/>
+      <c r="E44" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="33" customHeight="1">
+      <c r="B45" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D45" s="39"/>
+      <c r="E45" s="30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="33" customHeight="1">
+      <c r="B46" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D46" s="39"/>
+      <c r="E46" s="30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" ht="18" customHeight="1">
+      <c r="B47" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="39"/>
+      <c r="E47" s="30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" ht="33" customHeight="1">
+      <c r="B48" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D48" s="39"/>
+      <c r="E48" s="30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="18" customHeight="1">
+      <c r="B49" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" s="39"/>
+      <c r="E49" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="18" customHeight="1">
+      <c r="B50" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="40"/>
+      <c r="E50" s="28"/>
+    </row>
+    <row r="52" spans="1:5" ht="20" customHeight="1">
+      <c r="B52" s="41" t="s">
+        <v>3297</v>
+      </c>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+    </row>
+    <row r="53" spans="1:5" ht="20" customHeight="1">
+      <c r="B53" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C53" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D53" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" s="42"/>
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1">
+      <c r="B54" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54" s="43"/>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1">
+      <c r="B55" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D55" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="39"/>
+    </row>
+    <row r="56" spans="1:5" ht="33" customHeight="1">
+      <c r="B56" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D56" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="39"/>
+    </row>
+    <row r="57" spans="1:5" ht="18" customHeight="1">
+      <c r="B57" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D57" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="39"/>
+    </row>
+    <row r="58" spans="1:5" ht="18" customHeight="1">
+      <c r="B58" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D58" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="39"/>
+    </row>
+    <row r="59" spans="1:5" ht="33" customHeight="1">
+      <c r="B59" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E59" s="39"/>
+    </row>
+    <row r="60" spans="1:5" ht="18" customHeight="1">
+      <c r="B60" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D60" s="39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E60" s="39"/>
+    </row>
+    <row r="61" spans="1:5" ht="33" customHeight="1">
+      <c r="B61" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="40">
+        <v>62</v>
+      </c>
+      <c r="E61" s="40"/>
+    </row>
+    <row r="63" spans="1:5" ht="24" customHeight="1">
+      <c r="A63" s="36" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+    </row>
+    <row r="64" spans="1:5" ht="34" customHeight="1">
+      <c r="A64" s="38" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+    </row>
+    <row r="65" spans="1:5" ht="20" customHeight="1">
+      <c r="A65" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="D65" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="26" t="s">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="78" customHeight="1">
+      <c r="A66" s="29" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C66" s="27" t="s">
+        <v>3247</v>
+      </c>
+      <c r="D66" s="27" t="s">
+        <v>3248</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>3249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A67" s="35" t="s">
         <v>3286</v>
       </c>
-      <c r="C13" s="33" t="s">
-        <v>3287</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>3288</v>
-      </c>
-      <c r="E13" s="33"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="29" t="s">
-        <v>3290</v>
-      </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-    </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="B16" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-    </row>
-    <row r="17" spans="2:5" ht="18" customHeight="1">
-      <c r="B17" s="32" t="s">
-        <v>3291</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>3292</v>
-      </c>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-    </row>
-    <row r="18" spans="2:5" ht="33" customHeight="1">
-      <c r="B18" s="35" t="s">
-        <v>904</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-    </row>
-    <row r="19" spans="2:5" ht="18" customHeight="1">
-      <c r="B19" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-    </row>
-    <row r="20" spans="2:5" ht="18" customHeight="1">
-      <c r="B20" s="33" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="43" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-    </row>
-    <row r="22" spans="2:5" ht="20" customHeight="1">
-      <c r="B22" s="44" t="s">
-        <v>3293</v>
-      </c>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-    </row>
-    <row r="23" spans="2:5" ht="20" customHeight="1">
-      <c r="B23" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="40"/>
-      <c r="E23" s="31" t="s">
-        <v>3294</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" ht="18" customHeight="1">
-      <c r="B24" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="42" t="s">
-        <v>3295</v>
-      </c>
-      <c r="D24" s="42"/>
-      <c r="E24" s="32">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" ht="18" customHeight="1">
-      <c r="B25" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="41"/>
-      <c r="E25" s="35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="2:5" ht="18" customHeight="1">
-      <c r="B26" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="35">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" ht="18" customHeight="1">
-      <c r="B27" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="41"/>
-      <c r="E27" s="35">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="18" customHeight="1">
-      <c r="B28" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="41"/>
-      <c r="E28" s="35">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="18" customHeight="1">
-      <c r="B29" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="41"/>
-      <c r="E29" s="35">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="18" customHeight="1">
-      <c r="B30" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>3296</v>
-      </c>
-      <c r="D30" s="41"/>
-      <c r="E30" s="35">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="18" customHeight="1">
-      <c r="B31" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" s="41"/>
-      <c r="E31" s="35">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="18" customHeight="1">
-      <c r="B32" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" ht="33" customHeight="1">
-      <c r="B33" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="43"/>
-      <c r="E33" s="33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="20" customHeight="1">
-      <c r="B35" s="44" t="s">
-        <v>3297</v>
-      </c>
-      <c r="C35" s="44"/>
-      <c r="D35" s="44"/>
-      <c r="E35" s="44"/>
-    </row>
-    <row r="36" spans="2:5" ht="20" customHeight="1">
-      <c r="B36" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="D36" s="40"/>
-      <c r="E36" s="31" t="s">
-        <v>3298</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="42"/>
-      <c r="E37" s="32" t="s">
-        <v>3299</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" ht="18" customHeight="1">
-      <c r="B38" s="35" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="35" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" ht="18" customHeight="1">
-      <c r="B39" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="41"/>
-      <c r="E39" s="35" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="33" customHeight="1">
-      <c r="B40" s="35" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="41"/>
-      <c r="E40" s="35" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" ht="33" customHeight="1">
-      <c r="B41" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="41" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="41"/>
-      <c r="E41" s="35" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="18" customHeight="1">
-      <c r="B42" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="41"/>
-      <c r="E42" s="35" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="18" customHeight="1">
-      <c r="B43" s="35" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="41"/>
-      <c r="E43" s="35" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="18" customHeight="1">
-      <c r="B44" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="35">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" ht="33" customHeight="1">
-      <c r="B45" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="41"/>
-      <c r="E45" s="35" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" ht="33" customHeight="1">
-      <c r="B46" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" ht="18" customHeight="1">
-      <c r="B47" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="41"/>
-      <c r="E47" s="35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" ht="33" customHeight="1">
-      <c r="B48" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="35" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="B49" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="41"/>
-      <c r="E49" s="35" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="B50" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="43"/>
-      <c r="E50" s="33"/>
-    </row>
-    <row r="52" spans="1:5" ht="20" customHeight="1">
-      <c r="B52" s="44" t="s">
-        <v>3300</v>
-      </c>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-    </row>
-    <row r="53" spans="1:5" ht="20" customHeight="1">
-      <c r="B53" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" s="40"/>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="B54" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="D54" s="42" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="42"/>
-    </row>
-    <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="B55" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>65</v>
-      </c>
-      <c r="E55" s="41"/>
-    </row>
-    <row r="56" spans="1:5" ht="33" customHeight="1">
-      <c r="B56" s="35" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="41"/>
-    </row>
-    <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="B57" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="41"/>
-    </row>
-    <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="B58" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="41"/>
-    </row>
-    <row r="59" spans="1:5" ht="33" customHeight="1">
-      <c r="B59" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="41" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="41"/>
-    </row>
-    <row r="60" spans="1:5" ht="18" customHeight="1">
-      <c r="B60" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="41"/>
-    </row>
-    <row r="61" spans="1:5" ht="33" customHeight="1">
-      <c r="B61" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="43">
-        <v>62</v>
-      </c>
-      <c r="E61" s="43"/>
-    </row>
-    <row r="63" spans="1:5" ht="24" customHeight="1">
-      <c r="A63" s="29" t="s">
-        <v>3301</v>
-      </c>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-    </row>
-    <row r="64" spans="1:5" ht="34" customHeight="1">
-      <c r="A64" s="28" t="s">
-        <v>3302</v>
-      </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-    </row>
-    <row r="65" spans="1:5" ht="20" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C65" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="E65" s="31" t="s">
-        <v>3303</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="78" customHeight="1">
-      <c r="A66" s="34" t="s">
-        <v>3304</v>
-      </c>
-      <c r="B66" s="32" t="s">
-        <v>3246</v>
-      </c>
-      <c r="C66" s="32" t="s">
-        <v>3247</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>3248</v>
-      </c>
-      <c r="E66" s="32" t="s">
-        <v>3249</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A67" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="35" t="s">
+      <c r="C67" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="D67" s="35" t="s">
+      <c r="D67" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="E67" s="35" t="s">
+      <c r="E67" s="30" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A68" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B68" s="35" t="s">
+      <c r="A68" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B68" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C68" s="35" t="s">
+      <c r="C68" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="D68" s="35" t="s">
+      <c r="D68" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="E68" s="35" t="s">
+      <c r="E68" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A69" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B69" s="35" t="s">
+      <c r="A69" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B69" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C69" s="35" t="s">
+      <c r="C69" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D69" s="35" t="s">
+      <c r="D69" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="E69" s="35" t="s">
+      <c r="E69" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A70" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B70" s="35" t="s">
+      <c r="A70" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B70" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="35" t="s">
+      <c r="C70" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="D70" s="35" t="s">
+      <c r="D70" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="E70" s="35" t="s">
+      <c r="E70" s="30" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A71" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B71" s="35" t="s">
+      <c r="A71" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B71" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="C71" s="35" t="s">
+      <c r="C71" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="D71" s="35" t="s">
+      <c r="D71" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="E71" s="35" t="s">
+      <c r="E71" s="30" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="48" hidden="1" customHeight="1">
-      <c r="A72" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B72" s="35" t="s">
+      <c r="A72" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B72" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="C72" s="35" t="s">
+      <c r="C72" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="D72" s="35" t="s">
+      <c r="D72" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E72" s="35" t="s">
+      <c r="E72" s="30" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A73" s="45" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B73" s="35" t="s">
+      <c r="A73" s="35" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B73" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C73" s="35" t="s">
+      <c r="C73" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="35" t="s">
+      <c r="D73" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="35" t="s">
+      <c r="E73" s="30" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="33" hidden="1" customHeight="1">
-      <c r="A74" s="39" t="s">
-        <v>3289</v>
-      </c>
-      <c r="B74" s="33" t="s">
+      <c r="A74" s="34" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B74" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C74" s="33" t="s">
+      <c r="C74" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="33" t="s">
+      <c r="D74" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E74" s="33" t="s">
+      <c r="E74" s="28" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
     <mergeCell ref="A63:E63"/>
     <mergeCell ref="A64:E64"/>
     <mergeCell ref="D56:E56"/>
@@ -14038,48 +13775,6 @@
     <mergeCell ref="D59:E59"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="D61:E61"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C16:E16"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9E4A0F-D0F2-495C-8A3E-D322146F1317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71F60A9-138D-47AA-9D2F-178997F7D083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9802,9 +9802,6 @@
     <t>참고</t>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「꼭 수정」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
-  </si>
-  <si>
     <r>
       <t>할</t>
     </r>
@@ -9902,30 +9899,6 @@
   </si>
   <si>
     <t>policy goal_history_days · 설정 CFG-065 · 설정파라미터 CFG-065 · 검증규칙 V-45</t>
-  </si>
-  <si>
-    <r>
-      <t>꼭</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FFC00000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>수정</t>
-    </r>
   </si>
   <si>
     <t>목표 단계 오르기 정책값</t>
@@ -10557,6 +10530,14 @@
   </si>
   <si>
     <t>① 연구소 전달용 · 관리자 콘솔 diet-1.1.1(현재 적용 중)과 비교 · 2026-10-19</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10944,16 +10925,28 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10961,18 +10954,6 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12865,141 +12846,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="37" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+    </row>
+    <row r="2" spans="1:5" ht="34" customHeight="1">
+      <c r="A2" s="39" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="40" t="s">
         <v>3302</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-    </row>
-    <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+    </row>
+    <row r="5" spans="1:5" ht="19" customHeight="1">
+      <c r="A5" s="39" t="s">
         <v>3303</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="36" t="s">
-        <v>3304</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-    </row>
-    <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="38" t="s">
-        <v>3251</v>
-      </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="B5" s="39"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="26" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>3252</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>3253</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>3254</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>3255</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>3260</v>
+        <v>3304</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>3256</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>3257</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>3258</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>3259</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1">
       <c r="A8" s="31" t="s">
-        <v>3265</v>
+        <v>3263</v>
       </c>
       <c r="B8" s="30" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>3260</v>
+      </c>
+      <c r="D8" s="30" t="s">
         <v>3261</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="E8" s="30" t="s">
         <v>3262</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>3263</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>3264</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1">
       <c r="A9" s="32" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B9" s="30" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>3265</v>
+      </c>
+      <c r="D9" s="30" t="s">
         <v>3266</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="E9" s="30" t="s">
         <v>3267</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>3268</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>3269</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1">
       <c r="A10" s="32" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>3270</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="D10" s="30" t="s">
         <v>3271</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="E10" s="30" t="s">
         <v>3272</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>3273</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>3274</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="33" customHeight="1">
       <c r="A11" s="32" t="s">
-        <v>3270</v>
+        <v>3268</v>
       </c>
       <c r="B11" s="30" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>3274</v>
+      </c>
+      <c r="D11" s="30" t="s">
         <v>3275</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="E11" s="30" t="s">
         <v>3276</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>3277</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>3278</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" customHeight="1">
@@ -13007,58 +12988,58 @@
         <v>3250</v>
       </c>
       <c r="B12" s="30" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C12" s="30" t="s">
+        <v>3278</v>
+      </c>
+      <c r="D12" s="30" t="s">
         <v>3279</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="E12" s="30" t="s">
         <v>3280</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>3281</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>3282</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B13" s="28" t="s">
+        <v>3281</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>3282</v>
+      </c>
+      <c r="D13" s="28" t="s">
         <v>3283</v>
       </c>
-      <c r="C13" s="28" t="s">
-        <v>3284</v>
-      </c>
-      <c r="D13" s="28" t="s">
+      <c r="E13" s="28"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="40" t="s">
         <v>3285</v>
       </c>
-      <c r="E13" s="28"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>3287</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="B16" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
     </row>
     <row r="17" spans="2:5" ht="18" customHeight="1">
       <c r="B17" s="27" t="s">
-        <v>3288</v>
+        <v>3286</v>
       </c>
       <c r="C17" s="43" t="s">
-        <v>3289</v>
+        <v>3287</v>
       </c>
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
@@ -13067,50 +13048,50 @@
       <c r="B18" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1">
       <c r="B19" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="39" t="s">
+      <c r="C19" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1">
       <c r="B20" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="44" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
+      <c r="D20" s="44"/>
+      <c r="E20" s="44"/>
     </row>
     <row r="22" spans="2:5" ht="20" customHeight="1">
-      <c r="B22" s="41" t="s">
-        <v>3290</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
+      <c r="B22" s="45" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
     </row>
     <row r="23" spans="2:5" ht="20" customHeight="1">
       <c r="B23" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="42" t="s">
+      <c r="C23" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="42"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="26" t="s">
-        <v>3291</v>
+        <v>3289</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1">
@@ -13118,7 +13099,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>3292</v>
+        <v>3290</v>
       </c>
       <c r="D24" s="43"/>
       <c r="E24" s="27">
@@ -13129,10 +13110,10 @@
       <c r="B25" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="39"/>
+      <c r="D25" s="42"/>
       <c r="E25" s="30">
         <v>8</v>
       </c>
@@ -13141,10 +13122,10 @@
       <c r="B26" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="39"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="30">
         <v>14</v>
       </c>
@@ -13153,10 +13134,10 @@
       <c r="B27" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="39"/>
+      <c r="D27" s="42"/>
       <c r="E27" s="30">
         <v>61</v>
       </c>
@@ -13165,10 +13146,10 @@
       <c r="B28" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="39"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="30">
         <v>62</v>
       </c>
@@ -13177,10 +13158,10 @@
       <c r="B29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="39"/>
+      <c r="D29" s="42"/>
       <c r="E29" s="30">
         <v>63</v>
       </c>
@@ -13189,10 +13170,10 @@
       <c r="B30" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="39" t="s">
-        <v>3293</v>
-      </c>
-      <c r="D30" s="39"/>
+      <c r="C30" s="42" t="s">
+        <v>3291</v>
+      </c>
+      <c r="D30" s="42"/>
       <c r="E30" s="30">
         <v>403</v>
       </c>
@@ -13201,10 +13182,10 @@
       <c r="B31" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="39" t="s">
+      <c r="C31" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="39"/>
+      <c r="D31" s="42"/>
       <c r="E31" s="30">
         <v>20</v>
       </c>
@@ -13213,10 +13194,10 @@
       <c r="B32" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="39" t="s">
+      <c r="C32" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="39"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="30">
         <v>4</v>
       </c>
@@ -13225,32 +13206,32 @@
       <c r="B33" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="40"/>
+      <c r="D33" s="44"/>
       <c r="E33" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="20" customHeight="1">
-      <c r="B35" s="41" t="s">
-        <v>3294</v>
-      </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
+      <c r="B35" s="45" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
+      <c r="E35" s="45"/>
     </row>
     <row r="36" spans="2:5" ht="20" customHeight="1">
       <c r="B36" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C36" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="42"/>
+      <c r="D36" s="36"/>
       <c r="E36" s="26" t="s">
-        <v>3295</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="18" customHeight="1">
@@ -13262,17 +13243,17 @@
       </c>
       <c r="D37" s="43"/>
       <c r="E37" s="27" t="s">
-        <v>3296</v>
+        <v>3294</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="18" customHeight="1">
       <c r="B38" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="39"/>
+      <c r="D38" s="42"/>
       <c r="E38" s="30" t="s">
         <v>27</v>
       </c>
@@ -13281,10 +13262,10 @@
       <c r="B39" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="39"/>
+      <c r="D39" s="42"/>
       <c r="E39" s="30" t="s">
         <v>30</v>
       </c>
@@ -13293,10 +13274,10 @@
       <c r="B40" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="39"/>
+      <c r="D40" s="42"/>
       <c r="E40" s="30" t="s">
         <v>33</v>
       </c>
@@ -13305,10 +13286,10 @@
       <c r="B41" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="39"/>
+      <c r="D41" s="42"/>
       <c r="E41" s="30" t="s">
         <v>36</v>
       </c>
@@ -13317,10 +13298,10 @@
       <c r="B42" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="39"/>
+      <c r="D42" s="42"/>
       <c r="E42" s="30" t="s">
         <v>39</v>
       </c>
@@ -13329,10 +13310,10 @@
       <c r="B43" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="39"/>
+      <c r="D43" s="42"/>
       <c r="E43" s="30" t="s">
         <v>42</v>
       </c>
@@ -13341,10 +13322,10 @@
       <c r="B44" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="39"/>
+      <c r="D44" s="42"/>
       <c r="E44" s="30">
         <v>10</v>
       </c>
@@ -13353,10 +13334,10 @@
       <c r="B45" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="39"/>
+      <c r="D45" s="42"/>
       <c r="E45" s="30" t="s">
         <v>47</v>
       </c>
@@ -13365,10 +13346,10 @@
       <c r="B46" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="39"/>
+      <c r="D46" s="42"/>
       <c r="E46" s="30" t="s">
         <v>50</v>
       </c>
@@ -13377,10 +13358,10 @@
       <c r="B47" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="39"/>
+      <c r="D47" s="42"/>
       <c r="E47" s="30" t="s">
         <v>53</v>
       </c>
@@ -13389,10 +13370,10 @@
       <c r="B48" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="39"/>
+      <c r="D48" s="42"/>
       <c r="E48" s="30" t="s">
         <v>56</v>
       </c>
@@ -13401,10 +13382,10 @@
       <c r="B49" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="39"/>
+      <c r="D49" s="42"/>
       <c r="E49" s="30" t="s">
         <v>59</v>
       </c>
@@ -13413,19 +13394,19 @@
       <c r="B50" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="40" t="s">
+      <c r="C50" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="40"/>
+      <c r="D50" s="44"/>
       <c r="E50" s="28"/>
     </row>
     <row r="52" spans="1:5" ht="20" customHeight="1">
-      <c r="B52" s="41" t="s">
-        <v>3297</v>
-      </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
+      <c r="B52" s="45" t="s">
+        <v>3295</v>
+      </c>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="45"/>
     </row>
     <row r="53" spans="1:5" ht="20" customHeight="1">
       <c r="B53" s="26" t="s">
@@ -13434,10 +13415,10 @@
       <c r="C53" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="42" t="s">
+      <c r="D53" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="42"/>
+      <c r="E53" s="36"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
       <c r="B54" s="27" t="s">
@@ -13458,10 +13439,10 @@
       <c r="C55" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="39" t="s">
+      <c r="D55" s="42" t="s">
         <v>65</v>
       </c>
-      <c r="E55" s="39"/>
+      <c r="E55" s="42"/>
     </row>
     <row r="56" spans="1:5" ht="33" customHeight="1">
       <c r="B56" s="30" t="s">
@@ -13470,10 +13451,10 @@
       <c r="C56" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="39" t="s">
+      <c r="D56" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="39"/>
+      <c r="E56" s="42"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
       <c r="B57" s="30" t="s">
@@ -13482,10 +13463,10 @@
       <c r="C57" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="39" t="s">
+      <c r="D57" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="E57" s="39"/>
+      <c r="E57" s="42"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
       <c r="B58" s="30" t="s">
@@ -13494,10 +13475,10 @@
       <c r="C58" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="39" t="s">
+      <c r="D58" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="39"/>
+      <c r="E58" s="42"/>
     </row>
     <row r="59" spans="1:5" ht="33" customHeight="1">
       <c r="B59" s="30" t="s">
@@ -13506,10 +13487,10 @@
       <c r="C59" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="39" t="s">
+      <c r="D59" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="E59" s="39"/>
+      <c r="E59" s="42"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1">
       <c r="B60" s="30" t="s">
@@ -13518,10 +13499,10 @@
       <c r="C60" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="39" t="s">
+      <c r="D60" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="39"/>
+      <c r="E60" s="42"/>
     </row>
     <row r="61" spans="1:5" ht="33" customHeight="1">
       <c r="B61" s="28" t="s">
@@ -13530,28 +13511,28 @@
       <c r="C61" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="40">
+      <c r="D61" s="44">
         <v>62</v>
       </c>
-      <c r="E61" s="40"/>
+      <c r="E61" s="44"/>
     </row>
     <row r="63" spans="1:5" ht="24" customHeight="1">
-      <c r="A63" s="36" t="s">
-        <v>3298</v>
-      </c>
-      <c r="B63" s="37"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
+      <c r="A63" s="40" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B63" s="41"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="41"/>
     </row>
     <row r="64" spans="1:5" ht="34" customHeight="1">
-      <c r="A64" s="38" t="s">
-        <v>3299</v>
-      </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
+      <c r="A64" s="39" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B64" s="39"/>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
     </row>
     <row r="65" spans="1:5" ht="20" customHeight="1">
       <c r="A65" s="26" t="s">
@@ -13567,12 +13548,12 @@
         <v>82</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>3300</v>
+        <v>3298</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="78" customHeight="1">
       <c r="A66" s="29" t="s">
-        <v>3301</v>
+        <v>3299</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>3246</v>
@@ -13589,7 +13570,7 @@
     </row>
     <row r="67" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A67" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B67" s="30" t="s">
         <v>109</v>
@@ -13606,7 +13587,7 @@
     </row>
     <row r="68" spans="1:5" ht="108" hidden="1" customHeight="1">
       <c r="A68" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B68" s="30" t="s">
         <v>106</v>
@@ -13623,7 +13604,7 @@
     </row>
     <row r="69" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A69" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B69" s="30" t="s">
         <v>103</v>
@@ -13640,7 +13621,7 @@
     </row>
     <row r="70" spans="1:5" ht="123" hidden="1" customHeight="1">
       <c r="A70" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B70" s="30" t="s">
         <v>99</v>
@@ -13657,7 +13638,7 @@
     </row>
     <row r="71" spans="1:5" ht="303" hidden="1" customHeight="1">
       <c r="A71" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>95</v>
@@ -13674,7 +13655,7 @@
     </row>
     <row r="72" spans="1:5" ht="48" hidden="1" customHeight="1">
       <c r="A72" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B72" s="30" t="s">
         <v>91</v>
@@ -13691,7 +13672,7 @@
     </row>
     <row r="73" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A73" s="35" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B73" s="30" t="s">
         <v>87</v>
@@ -13708,7 +13689,7 @@
     </row>
     <row r="74" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A74" s="34" t="s">
-        <v>3286</v>
+        <v>3284</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>83</v>
@@ -13725,12 +13706,38 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
@@ -13743,38 +13750,12 @@
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C44:D44"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A71F60A9-138D-47AA-9D2F-178997F7D083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8269523A-150E-455F-9BB7-EB20068C6C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10689" uniqueCount="3305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10689" uniqueCount="3306">
   <si>
     <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.4.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
   </si>
@@ -9926,30 +9926,6 @@
   </si>
   <si>
     <t>서버 규칙 문서 11.1 · 문구 사용 이력</t>
-  </si>
-  <si>
-    <r>
-      <t>확인</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="Carlito"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF7F6000"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>필요</t>
-    </r>
   </si>
   <si>
     <t>규칙 문서 8.3 문구 고르기 설명</t>
@@ -10533,11 +10509,19 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「확인 필요」는 회신이 필요한 것입니다.</t>
+    <t>수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>수정 요청</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「답변 요청」은 회신만 주면 되는 것, 「문서 수정 요청」은 서버 규칙 문서를 고칠 것입니다.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>답변 요청</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>문서 수정 요청</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10694,13 +10678,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF7F6000"/>
-      <name val="Carlito"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF404040"/>
       <name val="Carlito"/>
     </font>
@@ -10730,8 +10707,14 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF5B3B8C"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10796,6 +10779,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -10830,7 +10819,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10916,17 +10905,38 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -10934,26 +10944,8 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12846,40 +12838,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="44" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+    </row>
+    <row r="2" spans="1:5" ht="34" customHeight="1">
+      <c r="A2" s="38" t="s">
         <v>3300</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-    </row>
-    <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1">
+      <c r="A4" s="36" t="s">
         <v>3301</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-    </row>
-    <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="40" t="s">
-        <v>3302</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="38" t="s">
         <v>3303</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="26" t="s">
@@ -12900,7 +12892,7 @@
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>3255</v>
@@ -12934,7 +12926,7 @@
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1">
       <c r="A9" s="32" t="s">
-        <v>3268</v>
+        <v>3304</v>
       </c>
       <c r="B9" s="30" t="s">
         <v>3264</v>
@@ -12950,37 +12942,37 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="46" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B10" s="30" t="s">
         <v>3268</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="C10" s="30" t="s">
         <v>3269</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="30" t="s">
         <v>3270</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="E10" s="30" t="s">
         <v>3271</v>
       </c>
-      <c r="E10" s="30" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="33" customHeight="1">
+      <c r="A11" s="46" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B11" s="30" t="s">
         <v>3272</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="32" t="s">
-        <v>3268</v>
-      </c>
-      <c r="B11" s="30" t="s">
+      <c r="C11" s="30" t="s">
         <v>3273</v>
       </c>
-      <c r="C11" s="30" t="s">
+      <c r="D11" s="30" t="s">
         <v>3274</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="E11" s="30" t="s">
         <v>3275</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>3276</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" customHeight="1">
@@ -12988,58 +12980,58 @@
         <v>3250</v>
       </c>
       <c r="B12" s="30" t="s">
+        <v>3276</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>3277</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="D12" s="30" t="s">
         <v>3278</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="E12" s="30" t="s">
         <v>3279</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>3280</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A13" s="34" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>3280</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>3281</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>3282</v>
+      </c>
+      <c r="E13" s="28"/>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1">
+      <c r="A15" s="36" t="s">
         <v>3284</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>3281</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>3282</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>3283</v>
-      </c>
-      <c r="E13" s="28"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="40" t="s">
-        <v>3285</v>
-      </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
+      <c r="B15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
     </row>
     <row r="16" spans="1:5" ht="20" customHeight="1">
       <c r="B16" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
     </row>
     <row r="17" spans="2:5" ht="18" customHeight="1">
       <c r="B17" s="27" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C17" s="43" t="s">
         <v>3286</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>3287</v>
       </c>
       <c r="D17" s="43"/>
       <c r="E17" s="43"/>
@@ -13048,50 +13040,50 @@
       <c r="B18" s="30" t="s">
         <v>904</v>
       </c>
-      <c r="C18" s="42" t="s">
+      <c r="C18" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" spans="2:5" ht="18" customHeight="1">
       <c r="B19" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1">
       <c r="B20" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
     </row>
     <row r="22" spans="2:5" ht="20" customHeight="1">
-      <c r="B22" s="45" t="s">
-        <v>3288</v>
-      </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
+      <c r="B22" s="41" t="s">
+        <v>3287</v>
+      </c>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
     </row>
     <row r="23" spans="2:5" ht="20" customHeight="1">
       <c r="B23" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="36"/>
+      <c r="D23" s="42"/>
       <c r="E23" s="26" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1">
@@ -13099,7 +13091,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="43" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="D24" s="43"/>
       <c r="E24" s="27">
@@ -13110,10 +13102,10 @@
       <c r="B25" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="42" t="s">
+      <c r="C25" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="42"/>
+      <c r="D25" s="39"/>
       <c r="E25" s="30">
         <v>8</v>
       </c>
@@ -13122,10 +13114,10 @@
       <c r="B26" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="42" t="s">
+      <c r="C26" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="42"/>
+      <c r="D26" s="39"/>
       <c r="E26" s="30">
         <v>14</v>
       </c>
@@ -13134,10 +13126,10 @@
       <c r="B27" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="42" t="s">
+      <c r="C27" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="42"/>
+      <c r="D27" s="39"/>
       <c r="E27" s="30">
         <v>61</v>
       </c>
@@ -13146,10 +13138,10 @@
       <c r="B28" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="D28" s="42"/>
+      <c r="D28" s="39"/>
       <c r="E28" s="30">
         <v>62</v>
       </c>
@@ -13158,10 +13150,10 @@
       <c r="B29" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="42" t="s">
+      <c r="C29" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="42"/>
+      <c r="D29" s="39"/>
       <c r="E29" s="30">
         <v>63</v>
       </c>
@@ -13170,10 +13162,10 @@
       <c r="B30" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="42" t="s">
-        <v>3291</v>
-      </c>
-      <c r="D30" s="42"/>
+      <c r="C30" s="39" t="s">
+        <v>3290</v>
+      </c>
+      <c r="D30" s="39"/>
       <c r="E30" s="30">
         <v>403</v>
       </c>
@@ -13182,10 +13174,10 @@
       <c r="B31" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="42" t="s">
+      <c r="C31" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D31" s="42"/>
+      <c r="D31" s="39"/>
       <c r="E31" s="30">
         <v>20</v>
       </c>
@@ -13194,10 +13186,10 @@
       <c r="B32" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="42" t="s">
+      <c r="C32" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="42"/>
+      <c r="D32" s="39"/>
       <c r="E32" s="30">
         <v>4</v>
       </c>
@@ -13206,32 +13198,32 @@
       <c r="B33" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C33" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="44"/>
+      <c r="D33" s="40"/>
       <c r="E33" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="35" spans="2:5" ht="20" customHeight="1">
-      <c r="B35" s="45" t="s">
-        <v>3292</v>
-      </c>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="45"/>
+      <c r="B35" s="41" t="s">
+        <v>3291</v>
+      </c>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41"/>
     </row>
     <row r="36" spans="2:5" ht="20" customHeight="1">
       <c r="B36" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="36"/>
+      <c r="D36" s="42"/>
       <c r="E36" s="26" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="37" spans="2:5" ht="18" customHeight="1">
@@ -13243,17 +13235,17 @@
       </c>
       <c r="D37" s="43"/>
       <c r="E37" s="27" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="18" customHeight="1">
       <c r="B38" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="42"/>
+      <c r="D38" s="39"/>
       <c r="E38" s="30" t="s">
         <v>27</v>
       </c>
@@ -13262,10 +13254,10 @@
       <c r="B39" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="42" t="s">
+      <c r="C39" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="42"/>
+      <c r="D39" s="39"/>
       <c r="E39" s="30" t="s">
         <v>30</v>
       </c>
@@ -13274,10 +13266,10 @@
       <c r="B40" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="42" t="s">
+      <c r="C40" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="42"/>
+      <c r="D40" s="39"/>
       <c r="E40" s="30" t="s">
         <v>33</v>
       </c>
@@ -13286,10 +13278,10 @@
       <c r="B41" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="42"/>
+      <c r="D41" s="39"/>
       <c r="E41" s="30" t="s">
         <v>36</v>
       </c>
@@ -13298,10 +13290,10 @@
       <c r="B42" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="D42" s="42"/>
+      <c r="D42" s="39"/>
       <c r="E42" s="30" t="s">
         <v>39</v>
       </c>
@@ -13310,10 +13302,10 @@
       <c r="B43" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="42"/>
+      <c r="D43" s="39"/>
       <c r="E43" s="30" t="s">
         <v>42</v>
       </c>
@@ -13322,10 +13314,10 @@
       <c r="B44" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="D44" s="42"/>
+      <c r="D44" s="39"/>
       <c r="E44" s="30">
         <v>10</v>
       </c>
@@ -13334,10 +13326,10 @@
       <c r="B45" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D45" s="42"/>
+      <c r="D45" s="39"/>
       <c r="E45" s="30" t="s">
         <v>47</v>
       </c>
@@ -13346,10 +13338,10 @@
       <c r="B46" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D46" s="42"/>
+      <c r="D46" s="39"/>
       <c r="E46" s="30" t="s">
         <v>50</v>
       </c>
@@ -13358,10 +13350,10 @@
       <c r="B47" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D47" s="42"/>
+      <c r="D47" s="39"/>
       <c r="E47" s="30" t="s">
         <v>53</v>
       </c>
@@ -13370,10 +13362,10 @@
       <c r="B48" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="D48" s="42"/>
+      <c r="D48" s="39"/>
       <c r="E48" s="30" t="s">
         <v>56</v>
       </c>
@@ -13382,10 +13374,10 @@
       <c r="B49" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="D49" s="42"/>
+      <c r="D49" s="39"/>
       <c r="E49" s="30" t="s">
         <v>59</v>
       </c>
@@ -13394,19 +13386,19 @@
       <c r="B50" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="44" t="s">
+      <c r="C50" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="D50" s="44"/>
+      <c r="D50" s="40"/>
       <c r="E50" s="28"/>
     </row>
     <row r="52" spans="1:5" ht="20" customHeight="1">
-      <c r="B52" s="45" t="s">
-        <v>3295</v>
-      </c>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
+      <c r="B52" s="41" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
     </row>
     <row r="53" spans="1:5" ht="20" customHeight="1">
       <c r="B53" s="26" t="s">
@@ -13415,10 +13407,10 @@
       <c r="C53" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="D53" s="36" t="s">
+      <c r="D53" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="E53" s="36"/>
+      <c r="E53" s="42"/>
     </row>
     <row r="54" spans="1:5" ht="18" customHeight="1">
       <c r="B54" s="27" t="s">
@@ -13439,10 +13431,10 @@
       <c r="C55" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="D55" s="42" t="s">
+      <c r="D55" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="E55" s="42"/>
+      <c r="E55" s="39"/>
     </row>
     <row r="56" spans="1:5" ht="33" customHeight="1">
       <c r="B56" s="30" t="s">
@@ -13451,10 +13443,10 @@
       <c r="C56" s="30" t="s">
         <v>66</v>
       </c>
-      <c r="D56" s="42" t="s">
+      <c r="D56" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="42"/>
+      <c r="E56" s="39"/>
     </row>
     <row r="57" spans="1:5" ht="18" customHeight="1">
       <c r="B57" s="30" t="s">
@@ -13463,10 +13455,10 @@
       <c r="C57" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D57" s="42" t="s">
+      <c r="D57" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E57" s="42"/>
+      <c r="E57" s="39"/>
     </row>
     <row r="58" spans="1:5" ht="18" customHeight="1">
       <c r="B58" s="30" t="s">
@@ -13475,10 +13467,10 @@
       <c r="C58" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="D58" s="42" t="s">
+      <c r="D58" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E58" s="42"/>
+      <c r="E58" s="39"/>
     </row>
     <row r="59" spans="1:5" ht="33" customHeight="1">
       <c r="B59" s="30" t="s">
@@ -13487,10 +13479,10 @@
       <c r="C59" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="D59" s="42" t="s">
+      <c r="D59" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E59" s="42"/>
+      <c r="E59" s="39"/>
     </row>
     <row r="60" spans="1:5" ht="18" customHeight="1">
       <c r="B60" s="30" t="s">
@@ -13499,10 +13491,10 @@
       <c r="C60" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D60" s="42" t="s">
+      <c r="D60" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="42"/>
+      <c r="E60" s="39"/>
     </row>
     <row r="61" spans="1:5" ht="33" customHeight="1">
       <c r="B61" s="28" t="s">
@@ -13511,28 +13503,28 @@
       <c r="C61" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D61" s="44">
+      <c r="D61" s="40">
         <v>62</v>
       </c>
-      <c r="E61" s="44"/>
+      <c r="E61" s="40"/>
     </row>
     <row r="63" spans="1:5" ht="24" customHeight="1">
-      <c r="A63" s="40" t="s">
+      <c r="A63" s="36" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+    </row>
+    <row r="64" spans="1:5" ht="34" customHeight="1">
+      <c r="A64" s="38" t="s">
         <v>3296</v>
       </c>
-      <c r="B63" s="41"/>
-      <c r="C63" s="41"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="41"/>
-    </row>
-    <row r="64" spans="1:5" ht="34" customHeight="1">
-      <c r="A64" s="39" t="s">
-        <v>3297</v>
-      </c>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
+      <c r="B64" s="38"/>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
     </row>
     <row r="65" spans="1:5" ht="20" customHeight="1">
       <c r="A65" s="26" t="s">
@@ -13548,12 +13540,12 @@
         <v>82</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="78" customHeight="1">
       <c r="A66" s="29" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="B66" s="27" t="s">
         <v>3246</v>
@@ -13570,7 +13562,7 @@
     </row>
     <row r="67" spans="1:5" ht="93" hidden="1" customHeight="1">
       <c r="A67" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B67" s="30" t="s">
         <v>109</v>
@@ -13587,7 +13579,7 @@
     </row>
     <row r="68" spans="1:5" ht="108" hidden="1" customHeight="1">
       <c r="A68" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B68" s="30" t="s">
         <v>106</v>
@@ -13604,7 +13596,7 @@
     </row>
     <row r="69" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A69" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B69" s="30" t="s">
         <v>103</v>
@@ -13621,7 +13613,7 @@
     </row>
     <row r="70" spans="1:5" ht="123" hidden="1" customHeight="1">
       <c r="A70" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B70" s="30" t="s">
         <v>99</v>
@@ -13638,7 +13630,7 @@
     </row>
     <row r="71" spans="1:5" ht="303" hidden="1" customHeight="1">
       <c r="A71" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B71" s="30" t="s">
         <v>95</v>
@@ -13655,7 +13647,7 @@
     </row>
     <row r="72" spans="1:5" ht="48" hidden="1" customHeight="1">
       <c r="A72" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B72" s="30" t="s">
         <v>91</v>
@@ -13672,7 +13664,7 @@
     </row>
     <row r="73" spans="1:5" ht="63" hidden="1" customHeight="1">
       <c r="A73" s="35" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B73" s="30" t="s">
         <v>87</v>
@@ -13689,7 +13681,7 @@
     </row>
     <row r="74" spans="1:5" ht="33" hidden="1" customHeight="1">
       <c r="A74" s="34" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>83</v>
@@ -13706,14 +13698,36 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A64:E64"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
@@ -13726,36 +13740,14 @@
     <mergeCell ref="B52:E52"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="D54:E54"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="D61:E61"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8269523A-150E-455F-9BB7-EB20068C6C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839EA437-9037-4640-BCE1-C626FF970C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10689" uniqueCount="3306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10669" uniqueCount="3287">
   <si>
     <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.4.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
   </si>
@@ -9797,9 +9797,6 @@
   </si>
   <si>
     <t>설정값 CFG-065 · 설정파라미터 CFG-065</t>
-  </si>
-  <si>
-    <t>참고</t>
   </si>
   <si>
     <r>
@@ -9914,54 +9911,6 @@
   </si>
   <si>
     <t>권장</t>
-  </si>
-  <si>
-    <t>버전이 바뀔 때 문구 사용 이력</t>
-  </si>
-  <si>
-    <t>규칙 문서 11.1: 버전이 바뀌면 문구 사용 이력도 새로 시작 → 새 버전마다 모든 사용자가 첫 문구부터 다시 봄</t>
-  </si>
-  <si>
-    <t>문구 내용이 같은 줄(문구 ID · 문구 버전이 같은 줄)은 이력을 이어 볼 수 있는지 회신</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 11.1 · 문구 사용 이력</t>
-  </si>
-  <si>
-    <t>규칙 문서 8.3 문구 고르기 설명</t>
-  </si>
-  <si>
-    <t>「최근 30일 안 쓴 문구 → 오래전에 쓴 문구 → 데이터 순서」로 적혀 「안 쓴 문구가 먼저」로 읽힘</t>
-  </si>
-  <si>
-    <t>실제 동작대로 고침: 조회 기간 밖 문구와 안 쓴 문구를 같이 놓고 데이터 순서로 고름. 조회 기간 마지막 날(정확히 30일 전)에 쓴 문구도 「최근」으로 봄</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 8.3</t>
-  </si>
-  <si>
-    <t>규칙 문서 예시</t>
-  </si>
-  <si>
-    <t>8.4 · 5장 예시가 1.0.4 기준</t>
-  </si>
-  <si>
-    <t>1.1.1 기준으로 고침(예: 「국 대신 나물 반찬」은 채소 기본 단계, 새벽 3시에 「내일 채소 꺼내 두기」가 나옴)</t>
-  </si>
-  <si>
-    <t>서버 규칙 문서 5.4 · 8.4</t>
-  </si>
-  <si>
-    <t>영어 사용자 긴 문장 · 이유</t>
-  </si>
-  <si>
-    <t>title_text_full_context_en · reason_text_en 403개 모두 비어 있어 영어 목표 카드에 짧은 문구만 나옴</t>
-  </si>
-  <si>
-    <t>영문 번역은 우리가 정리해 다음에 전달함. 이번에 바꿀 것 없음</t>
-  </si>
-  <si>
-    <t>goal_phrases title_text_full_context_en · reason_text_en</t>
   </si>
   <si>
     <t>나머지</t>
@@ -10513,15 +10462,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」 「권장」은 데이터를 바꿀 것, 「답변 요청」은 회신만 주면 되는 것, 「문서 수정 요청」은 서버 규칙 문서를 고칠 것입니다.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>답변 요청</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>문서 수정 요청</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것, 「권장」은 바꾸면 좋은 것입니다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10529,7 +10470,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="31">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10672,18 +10613,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF7F6000"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF404040"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Carlito"/>
     </font>
@@ -10707,14 +10636,8 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF5B3B8C"/>
-      <name val="Carlito"/>
-    </font>
   </fonts>
-  <fills count="13">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10745,18 +10668,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEDEDED"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -10776,12 +10687,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4DFEC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10819,7 +10724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10884,7 +10789,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10899,25 +10804,19 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10929,10 +10828,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10943,9 +10842,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12826,7 +12722,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.58203125" style="25" customWidth="1"/>
@@ -12838,916 +12734,848 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="44" t="s">
-        <v>3299</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
+      <c r="A1" s="42" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>3300</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
+      <c r="A2" s="36" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="36" t="s">
-        <v>3301</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="A4" s="34" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
-      <c r="A5" s="38" t="s">
-        <v>3303</v>
-      </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
+      <c r="A5" s="36" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
     </row>
     <row r="6" spans="1:5" ht="20" customHeight="1">
       <c r="A6" s="26" t="s">
         <v>28</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>3250</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>3251</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>3252</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>3253</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>3254</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>3302</v>
+        <v>3285</v>
       </c>
       <c r="B7" s="27" t="s">
+        <v>3254</v>
+      </c>
+      <c r="C7" s="27" t="s">
         <v>3255</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="D7" s="27" t="s">
         <v>3256</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="E7" s="27" t="s">
         <v>3257</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>3258</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1">
       <c r="A8" s="31" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>3258</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>3259</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>3260</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>3261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="78" hidden="1" customHeight="1">
+      <c r="A9" s="32" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B9" s="28" t="s">
         <v>3263</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>3259</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>3260</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>3261</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>3262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="48" customHeight="1">
-      <c r="A9" s="32" t="s">
-        <v>3304</v>
-      </c>
-      <c r="B9" s="30" t="s">
+      <c r="C9" s="28" t="s">
         <v>3264</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="D9" s="28" t="s">
         <v>3265</v>
       </c>
-      <c r="D9" s="30" t="s">
-        <v>3266</v>
-      </c>
-      <c r="E9" s="30" t="s">
+      <c r="E9" s="28"/>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1">
+      <c r="A11" s="34" t="s">
         <v>3267</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="48" customHeight="1">
-      <c r="A10" s="46" t="s">
-        <v>3305</v>
-      </c>
-      <c r="B10" s="30" t="s">
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" spans="1:5" ht="20" customHeight="1">
+      <c r="B12" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+    </row>
+    <row r="13" spans="1:5" ht="18" customHeight="1">
+      <c r="B13" s="27" t="s">
         <v>3268</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C13" s="41" t="s">
         <v>3269</v>
       </c>
-      <c r="D10" s="30" t="s">
-        <v>3270</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>3271</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="33" customHeight="1">
-      <c r="A11" s="46" t="s">
-        <v>3305</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>3272</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>3273</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>3274</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>3275</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="48" customHeight="1">
-      <c r="A12" s="33" t="s">
-        <v>3250</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>3276</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>3277</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>3278</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>3279</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A13" s="34" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B13" s="28" t="s">
-        <v>3280</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>3281</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>3282</v>
-      </c>
-      <c r="E13" s="28"/>
-    </row>
-    <row r="15" spans="1:5" ht="24" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>3284</v>
-      </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+    </row>
+    <row r="14" spans="1:5" ht="33" customHeight="1">
+      <c r="B14" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:5" ht="18" customHeight="1">
+      <c r="B15" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>77</v>
+      </c>
       <c r="D15" s="37"/>
       <c r="E15" s="37"/>
     </row>
-    <row r="16" spans="1:5" ht="20" customHeight="1">
-      <c r="B16" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-    </row>
-    <row r="17" spans="2:5" ht="18" customHeight="1">
-      <c r="B17" s="27" t="s">
-        <v>3285</v>
-      </c>
-      <c r="C17" s="43" t="s">
-        <v>3286</v>
-      </c>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-    </row>
-    <row r="18" spans="2:5" ht="33" customHeight="1">
-      <c r="B18" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>0</v>
-      </c>
+    <row r="16" spans="1:5" ht="18" customHeight="1">
+      <c r="B16" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+    </row>
+    <row r="18" spans="2:5" ht="20" customHeight="1">
+      <c r="B18" s="39" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C18" s="39"/>
       <c r="D18" s="39"/>
       <c r="E18" s="39"/>
     </row>
-    <row r="19" spans="2:5" ht="18" customHeight="1">
-      <c r="B19" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
+    <row r="19" spans="2:5" ht="20" customHeight="1">
+      <c r="B19" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="40"/>
+      <c r="E19" s="26" t="s">
+        <v>3271</v>
+      </c>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1">
-      <c r="B20" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-    </row>
-    <row r="22" spans="2:5" ht="20" customHeight="1">
-      <c r="B22" s="41" t="s">
-        <v>3287</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-    </row>
-    <row r="23" spans="2:5" ht="20" customHeight="1">
-      <c r="B23" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C23" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="D23" s="42"/>
-      <c r="E23" s="26" t="s">
-        <v>3288</v>
+      <c r="B20" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>3272</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="27">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" ht="18" customHeight="1">
+      <c r="B21" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" ht="18" customHeight="1">
+      <c r="B22" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="37"/>
+      <c r="E22" s="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" ht="18" customHeight="1">
+      <c r="B23" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="37"/>
+      <c r="E23" s="30">
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1">
-      <c r="B24" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>3289</v>
-      </c>
-      <c r="D24" s="43"/>
-      <c r="E24" s="27">
-        <v>403</v>
+      <c r="B24" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="37"/>
+      <c r="E24" s="30">
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="18" customHeight="1">
       <c r="B25" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="39"/>
+        <v>12</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="37"/>
       <c r="E25" s="30">
-        <v>8</v>
+        <v>63</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="18" customHeight="1">
       <c r="B26" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="39"/>
+        <v>14</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>3273</v>
+      </c>
+      <c r="D26" s="37"/>
       <c r="E26" s="30">
-        <v>14</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="18" customHeight="1">
       <c r="B27" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="39"/>
+        <v>15</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="37"/>
       <c r="E27" s="30">
-        <v>61</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="18" customHeight="1">
       <c r="B28" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="39"/>
+        <v>17</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="37"/>
       <c r="E28" s="30">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="2:5" ht="18" customHeight="1">
-      <c r="B29" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="D29" s="39"/>
-      <c r="E29" s="30">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="18" customHeight="1">
-      <c r="B30" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>3290</v>
-      </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="30">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5" ht="18" customHeight="1">
-      <c r="B31" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>16</v>
-      </c>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="33" customHeight="1">
+      <c r="B29" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="38"/>
+      <c r="E29" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" ht="20" customHeight="1">
+      <c r="B31" s="39" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C31" s="39"/>
       <c r="D31" s="39"/>
-      <c r="E31" s="30">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" ht="18" customHeight="1">
-      <c r="B32" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" ht="33" customHeight="1">
-      <c r="B33" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="40"/>
-      <c r="E33" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="20" customHeight="1">
-      <c r="B35" s="41" t="s">
-        <v>3291</v>
-      </c>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-    </row>
-    <row r="36" spans="2:5" ht="20" customHeight="1">
-      <c r="B36" s="26" t="s">
+      <c r="E31" s="39"/>
+    </row>
+    <row r="32" spans="2:5" ht="20" customHeight="1">
+      <c r="B32" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C32" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="D36" s="42"/>
-      <c r="E36" s="26" t="s">
-        <v>3292</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="27" t="s">
+      <c r="D32" s="40"/>
+      <c r="E32" s="26" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" ht="18" customHeight="1">
+      <c r="B33" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C37" s="43" t="s">
+      <c r="C33" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="27" t="s">
-        <v>3293</v>
+      <c r="D33" s="41"/>
+      <c r="E33" s="27" t="s">
+        <v>3276</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" ht="18" customHeight="1">
+      <c r="B34" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" s="37"/>
+      <c r="E34" s="30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="18" customHeight="1">
+      <c r="B35" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="37"/>
+      <c r="E35" s="30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" ht="33" customHeight="1">
+      <c r="B36" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="37"/>
+      <c r="E36" s="30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="33" customHeight="1">
+      <c r="B37" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="37"/>
+      <c r="E37" s="30" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="18" customHeight="1">
       <c r="B38" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="39"/>
+        <v>37</v>
+      </c>
+      <c r="C38" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="37"/>
       <c r="E38" s="30" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="18" customHeight="1">
       <c r="B39" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="39"/>
+        <v>40</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="37"/>
       <c r="E39" s="30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="33" customHeight="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="18" customHeight="1">
       <c r="B40" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="D40" s="39"/>
-      <c r="E40" s="30" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="C40" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="37"/>
+      <c r="E40" s="30">
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="33" customHeight="1">
       <c r="B41" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="39" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="39"/>
+        <v>45</v>
+      </c>
+      <c r="C41" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="37"/>
       <c r="E41" s="30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="18" customHeight="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="33" customHeight="1">
       <c r="B42" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="39"/>
+        <v>48</v>
+      </c>
+      <c r="C42" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="37"/>
       <c r="E42" s="30" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="2:5" ht="18" customHeight="1">
       <c r="B43" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" s="39"/>
+        <v>51</v>
+      </c>
+      <c r="C43" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="37"/>
       <c r="E43" s="30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="18" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="33" customHeight="1">
       <c r="B44" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="39"/>
-      <c r="E44" s="30">
+        <v>54</v>
+      </c>
+      <c r="C44" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D44" s="37"/>
+      <c r="E44" s="30" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" ht="18" customHeight="1">
+      <c r="B45" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="37"/>
+      <c r="E45" s="30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" ht="18" customHeight="1">
+      <c r="B46" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="38"/>
+      <c r="E46" s="28"/>
+    </row>
+    <row r="48" spans="2:5" ht="20" customHeight="1">
+      <c r="B48" s="39" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39"/>
+      <c r="E48" s="39"/>
+    </row>
+    <row r="49" spans="1:5" ht="20" customHeight="1">
+      <c r="B49" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="D49" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" s="40"/>
+    </row>
+    <row r="50" spans="1:5" ht="18" customHeight="1">
+      <c r="B50" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D50" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="E50" s="41"/>
+    </row>
+    <row r="51" spans="1:5" ht="18" customHeight="1">
+      <c r="B51" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="37"/>
+    </row>
+    <row r="52" spans="1:5" ht="33" customHeight="1">
+      <c r="B52" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="37"/>
+    </row>
+    <row r="53" spans="1:5" ht="18" customHeight="1">
+      <c r="B53" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E53" s="37"/>
+    </row>
+    <row r="54" spans="1:5" ht="18" customHeight="1">
+      <c r="B54" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="37"/>
+    </row>
+    <row r="55" spans="1:5" ht="33" customHeight="1">
+      <c r="B55" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="E55" s="37"/>
+    </row>
+    <row r="56" spans="1:5" ht="18" customHeight="1">
+      <c r="B56" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D56" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56" s="37"/>
+    </row>
+    <row r="57" spans="1:5" ht="33" customHeight="1">
+      <c r="B57" s="28" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" ht="33" customHeight="1">
-      <c r="B45" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="39"/>
-      <c r="E45" s="30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" ht="33" customHeight="1">
-      <c r="B46" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="39"/>
-      <c r="E46" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" ht="18" customHeight="1">
-      <c r="B47" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" ht="33" customHeight="1">
-      <c r="B48" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="39" t="s">
-        <v>55</v>
-      </c>
-      <c r="D48" s="39"/>
-      <c r="E48" s="30" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="18" customHeight="1">
-      <c r="B49" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D49" s="39"/>
-      <c r="E49" s="30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="B50" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="40"/>
-      <c r="E50" s="28"/>
-    </row>
-    <row r="52" spans="1:5" ht="20" customHeight="1">
-      <c r="B52" s="41" t="s">
-        <v>3294</v>
-      </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-    </row>
-    <row r="53" spans="1:5" ht="20" customHeight="1">
-      <c r="B53" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C53" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="E53" s="42"/>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="B54" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="C54" s="27" t="s">
+      <c r="C57" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="38">
         <v>62</v>
       </c>
-      <c r="D54" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="E54" s="43"/>
-    </row>
-    <row r="55" spans="1:5" ht="18" customHeight="1">
-      <c r="B55" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D55" s="39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E55" s="39"/>
-    </row>
-    <row r="56" spans="1:5" ht="33" customHeight="1">
-      <c r="B56" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C56" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="39"/>
-    </row>
-    <row r="57" spans="1:5" ht="18" customHeight="1">
-      <c r="B57" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D57" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="39"/>
-    </row>
-    <row r="58" spans="1:5" ht="18" customHeight="1">
-      <c r="B58" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D58" s="39" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="39"/>
-    </row>
-    <row r="59" spans="1:5" ht="33" customHeight="1">
-      <c r="B59" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D59" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="E59" s="39"/>
-    </row>
-    <row r="60" spans="1:5" ht="18" customHeight="1">
-      <c r="B60" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D60" s="39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E60" s="39"/>
-    </row>
-    <row r="61" spans="1:5" ht="33" customHeight="1">
-      <c r="B61" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="40">
-        <v>62</v>
-      </c>
-      <c r="E61" s="40"/>
-    </row>
-    <row r="63" spans="1:5" ht="24" customHeight="1">
-      <c r="A63" s="36" t="s">
-        <v>3295</v>
-      </c>
-      <c r="B63" s="37"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-    </row>
-    <row r="64" spans="1:5" ht="34" customHeight="1">
-      <c r="A64" s="38" t="s">
-        <v>3296</v>
-      </c>
-      <c r="B64" s="38"/>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-    </row>
-    <row r="65" spans="1:5" ht="20" customHeight="1">
-      <c r="A65" s="26" t="s">
+      <c r="E57" s="38"/>
+    </row>
+    <row r="59" spans="1:5" ht="24" customHeight="1">
+      <c r="A59" s="34" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="35"/>
+    </row>
+    <row r="60" spans="1:5" ht="34" customHeight="1">
+      <c r="A60" s="36" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B60" s="36"/>
+      <c r="C60" s="36"/>
+      <c r="D60" s="36"/>
+      <c r="E60" s="36"/>
+    </row>
+    <row r="61" spans="1:5" ht="20" customHeight="1">
+      <c r="A61" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B65" s="26" t="s">
+      <c r="B61" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C61" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="D65" s="26" t="s">
+      <c r="D61" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E65" s="26" t="s">
-        <v>3297</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="78" customHeight="1">
-      <c r="A66" s="29" t="s">
-        <v>3298</v>
-      </c>
-      <c r="B66" s="27" t="s">
+      <c r="E61" s="26" t="s">
+        <v>3280</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="78" customHeight="1">
+      <c r="A62" s="29" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>3246</v>
       </c>
-      <c r="C66" s="27" t="s">
+      <c r="C62" s="27" t="s">
         <v>3247</v>
       </c>
-      <c r="D66" s="27" t="s">
+      <c r="D62" s="27" t="s">
         <v>3248</v>
       </c>
-      <c r="E66" s="27" t="s">
+      <c r="E62" s="27" t="s">
         <v>3249</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A67" s="35" t="s">
-        <v>3283</v>
+    <row r="63" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A63" s="33" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="108" hidden="1" customHeight="1">
+      <c r="A64" s="33" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="D64" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="63" hidden="1" customHeight="1">
+      <c r="A65" s="33" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E65" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="123" hidden="1" customHeight="1">
+      <c r="A66" s="33" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="E66" s="30" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="303" hidden="1" customHeight="1">
+      <c r="A67" s="33" t="s">
+        <v>3266</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A68" s="35" t="s">
-        <v>3283</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="48" hidden="1" customHeight="1">
+      <c r="A68" s="33" t="s">
+        <v>3266</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A69" s="35" t="s">
-        <v>3283</v>
+      <c r="A69" s="33" t="s">
+        <v>3266</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E69" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A70" s="35" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B70" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A71" s="35" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B71" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="D71" s="30" t="s">
-        <v>97</v>
-      </c>
-      <c r="E71" s="30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="48" hidden="1" customHeight="1">
-      <c r="A72" s="35" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B72" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C72" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D72" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="E72" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A73" s="35" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B73" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C73" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E73" s="30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="33" hidden="1" customHeight="1">
-      <c r="A74" s="34" t="s">
-        <v>3283</v>
-      </c>
-      <c r="B74" s="28" t="s">
+    <row r="70" spans="1:5" ht="33" hidden="1" customHeight="1">
+      <c r="A70" s="32" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B70" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C74" s="28" t="s">
+      <c r="C70" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="28" t="s">
+      <c r="D70" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E74" s="28" t="s">
+      <c r="E70" s="28" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C12:E12"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A15:E15"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B31:E31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="D51:E51"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="D52:E52"/>
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="D54:E54"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A64:E64"/>
+    <mergeCell ref="D55:E55"/>
     <mergeCell ref="D56:E56"/>
     <mergeCell ref="D57:E57"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="D61:E61"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
+++ b/전달/2026-10-19_연구소_식이데이터계약/maiReport_식이_참조설정데이터_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\전달\2026-10-19_연구소_식이데이터계약\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839EA437-9037-4640-BCE1-C626FF970C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278559C6-B83F-40D5-B1A3-DF06F257E04F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10669" uniqueCount="3287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10664" uniqueCount="3282">
   <si>
     <t>v1.0.0 발행 뒤 고친 내용을 반영한 v1.4.0입니다. 바뀐 것은 아래 「바뀐 내용」 표에 있습니다. 식이 문구 403개, 질문, 질환 규칙, 설정 기준을 제공합니다. 검진일로부터 3개월 이내 신호만 기존 식이 축에 연결합니다.</t>
   </si>
@@ -9896,21 +9896,6 @@
   </si>
   <si>
     <t>policy goal_history_days · 설정 CFG-065 · 설정파라미터 CFG-065 · 검증규칙 V-45</t>
-  </si>
-  <si>
-    <t>목표 단계 오르기 정책값</t>
-  </si>
-  <si>
-    <t>policy에 stage_up_window_days 7이 남아 있음. 실제 동작은 코드 상수(최근 4건 · 완료 3건 · 56일)로 계약과 같음</t>
-  </si>
-  <si>
-    <t>정책값을 계약에 맞춰 옮김: 최근 목표 4건 중 완료 3건 · 끝난 목표 3건 이상 · 56일 · 최근 2건 연속 미완료면 내림 · 관찰 중 축은 안 오름 · 개선 필요는 기본까지</t>
-  </si>
-  <si>
-    <t>policy · 설정파라미터 CFG-010 · CFG-011 · CFG-068 · CFG-069 · CFG-071</t>
-  </si>
-  <si>
-    <t>권장</t>
   </si>
   <si>
     <t>나머지</t>
@@ -10462,7 +10447,7 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것, 「권장」은 바꾸면 좋은 것입니다.</t>
+    <t>질문 · 선택지 · 목표 문구 403개 · 질환 표 · 달력은 1.1.1과 같습니다. 아래 줄만 다릅니다. 「수정 요청」은 꼭 바꿀 것입니다.</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -10470,7 +10455,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -10607,12 +10592,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFC55911"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF375623"/>
       <name val="Carlito"/>
     </font>
@@ -10637,7 +10616,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10684,12 +10663,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -10724,7 +10697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -10804,14 +10777,23 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -10819,29 +10801,17 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12722,7 +12692,7 @@
   <sheetPr>
     <tabColor rgb="FF1F4E79"/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.58203125" style="25" customWidth="1"/>
@@ -12734,17 +12704,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>3282</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
+      <c r="A1" s="34" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
     </row>
     <row r="2" spans="1:5" ht="34" customHeight="1">
       <c r="A2" s="36" t="s">
-        <v>3283</v>
+        <v>3278</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -12752,17 +12722,17 @@
       <c r="E2" s="36"/>
     </row>
     <row r="4" spans="1:5" ht="24" customHeight="1">
-      <c r="A4" s="34" t="s">
-        <v>3284</v>
-      </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+      <c r="A4" s="37" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
     </row>
     <row r="5" spans="1:5" ht="19" customHeight="1">
       <c r="A5" s="36" t="s">
-        <v>3286</v>
+        <v>3281</v>
       </c>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -12788,7 +12758,7 @@
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>3285</v>
+        <v>3280</v>
       </c>
       <c r="B7" s="27" t="s">
         <v>3254</v>
@@ -12803,760 +12773,722 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="48" customHeight="1">
+    <row r="8" spans="1:5" ht="78" hidden="1" customHeight="1">
       <c r="A8" s="31" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>3258</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>3259</v>
+      </c>
+      <c r="D8" s="28" t="s">
+        <v>3260</v>
+      </c>
+      <c r="E8" s="28"/>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1">
+      <c r="A10" s="37" t="s">
         <v>3262</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>3258</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>3259</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>3260</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>3261</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="78" hidden="1" customHeight="1">
-      <c r="A9" s="32" t="s">
-        <v>3266</v>
-      </c>
-      <c r="B9" s="28" t="s">
+      <c r="B10" s="38"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+    </row>
+    <row r="11" spans="1:5" ht="20" customHeight="1">
+      <c r="B11" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+    </row>
+    <row r="12" spans="1:5" ht="18" customHeight="1">
+      <c r="B12" s="27" t="s">
         <v>3263</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C12" s="40" t="s">
         <v>3264</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>3265</v>
-      </c>
-      <c r="E9" s="28"/>
-    </row>
-    <row r="11" spans="1:5" ht="24" customHeight="1">
-      <c r="A11" s="34" t="s">
-        <v>3267</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12" spans="1:5" ht="20" customHeight="1">
-      <c r="B12" s="26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>2</v>
       </c>
       <c r="D12" s="40"/>
       <c r="E12" s="40"/>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1">
-      <c r="B13" s="27" t="s">
-        <v>3268</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>3269</v>
-      </c>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-    </row>
-    <row r="14" spans="1:5" ht="33" customHeight="1">
+    <row r="13" spans="1:5" ht="33" customHeight="1">
+      <c r="B13" s="30" t="s">
+        <v>904</v>
+      </c>
+      <c r="C13" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+    </row>
+    <row r="14" spans="1:5" ht="18" customHeight="1">
       <c r="B14" s="30" t="s">
-        <v>904</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
+        <v>76</v>
+      </c>
+      <c r="C14" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1">
-      <c r="B15" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-    </row>
-    <row r="16" spans="1:5" ht="18" customHeight="1">
-      <c r="B16" s="28" t="s">
+      <c r="B15" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C15" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+    </row>
+    <row r="17" spans="2:5" ht="20" customHeight="1">
+      <c r="B17" s="42" t="s">
+        <v>3265</v>
+      </c>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
     </row>
     <row r="18" spans="2:5" ht="20" customHeight="1">
-      <c r="B18" s="39" t="s">
-        <v>3270</v>
-      </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-    </row>
-    <row r="19" spans="2:5" ht="20" customHeight="1">
-      <c r="B19" s="26" t="s">
+      <c r="B18" s="26" t="s">
         <v>1</v>
       </c>
+      <c r="C18" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="33"/>
+      <c r="E18" s="26" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="18" customHeight="1">
+      <c r="B19" s="27" t="s">
+        <v>3</v>
+      </c>
       <c r="C19" s="40" t="s">
-        <v>2</v>
+        <v>3267</v>
       </c>
       <c r="D19" s="40"/>
-      <c r="E19" s="26" t="s">
-        <v>3271</v>
+      <c r="E19" s="27">
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="18" customHeight="1">
-      <c r="B20" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>3272</v>
-      </c>
-      <c r="D20" s="41"/>
-      <c r="E20" s="27">
-        <v>403</v>
+      <c r="B20" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="39"/>
+      <c r="E20" s="30">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="18" customHeight="1">
       <c r="B21" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="37"/>
+        <v>6</v>
+      </c>
+      <c r="C21" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="39"/>
       <c r="E21" s="30">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="18" customHeight="1">
       <c r="B22" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="37"/>
+        <v>8</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="39"/>
       <c r="E22" s="30">
-        <v>14</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="18" customHeight="1">
       <c r="B23" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="37"/>
+        <v>10</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="39"/>
       <c r="E23" s="30">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="18" customHeight="1">
       <c r="B24" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="37"/>
+        <v>12</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="39"/>
       <c r="E24" s="30">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="18" customHeight="1">
       <c r="B25" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="37" t="s">
-        <v>13</v>
-      </c>
-      <c r="D25" s="37"/>
+        <v>14</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D25" s="39"/>
       <c r="E25" s="30">
-        <v>63</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="18" customHeight="1">
       <c r="B26" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>3273</v>
-      </c>
-      <c r="D26" s="37"/>
+        <v>15</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="39"/>
       <c r="E26" s="30">
-        <v>403</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="18" customHeight="1">
       <c r="B27" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="D27" s="37"/>
+        <v>17</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="39"/>
       <c r="E27" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" ht="33" customHeight="1">
+      <c r="B28" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="41" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" ht="18" customHeight="1">
-      <c r="B28" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D28" s="37"/>
-      <c r="E28" s="30">
+      <c r="D28" s="41"/>
+      <c r="E28" s="28">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="33" customHeight="1">
-      <c r="B29" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="38"/>
-      <c r="E29" s="28">
-        <v>4</v>
-      </c>
+    <row r="30" spans="2:5" ht="20" customHeight="1">
+      <c r="B30" s="42" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
     </row>
     <row r="31" spans="2:5" ht="20" customHeight="1">
-      <c r="B31" s="39" t="s">
-        <v>3274</v>
-      </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-    </row>
-    <row r="32" spans="2:5" ht="20" customHeight="1">
-      <c r="B32" s="26" t="s">
+      <c r="B31" s="26" t="s">
         <v>21</v>
       </c>
+      <c r="C31" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="D31" s="33"/>
+      <c r="E31" s="26" t="s">
+        <v>3270</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" ht="18" customHeight="1">
+      <c r="B32" s="27" t="s">
+        <v>23</v>
+      </c>
       <c r="C32" s="40" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D32" s="40"/>
-      <c r="E32" s="26" t="s">
-        <v>3275</v>
+      <c r="E32" s="27" t="s">
+        <v>3271</v>
       </c>
     </row>
     <row r="33" spans="2:5" ht="18" customHeight="1">
-      <c r="B33" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="41"/>
-      <c r="E33" s="27" t="s">
-        <v>3276</v>
+      <c r="B33" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" s="39"/>
+      <c r="E33" s="30" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="2:5" ht="18" customHeight="1">
       <c r="B34" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="37"/>
+        <v>28</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="39"/>
       <c r="E34" s="30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" ht="18" customHeight="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" ht="33" customHeight="1">
       <c r="B35" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="37"/>
+        <v>31</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="39"/>
       <c r="E35" s="30" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="2:5" ht="33" customHeight="1">
       <c r="B36" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="37"/>
+        <v>34</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="39"/>
       <c r="E36" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" ht="33" customHeight="1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" ht="18" customHeight="1">
       <c r="B37" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="37"/>
+        <v>37</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="39"/>
       <c r="E37" s="30" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="2:5" ht="18" customHeight="1">
       <c r="B38" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="37"/>
+        <v>40</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="39"/>
       <c r="E38" s="30" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="2:5" ht="18" customHeight="1">
       <c r="B39" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="37"/>
-      <c r="E39" s="30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" ht="18" customHeight="1">
+        <v>43</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="39"/>
+      <c r="E39" s="30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" ht="33" customHeight="1">
       <c r="B40" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="37"/>
-      <c r="E40" s="30">
-        <v>10</v>
+        <v>45</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="39"/>
+      <c r="E40" s="30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="33" customHeight="1">
       <c r="B41" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="37" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="37"/>
+        <v>48</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" s="39"/>
       <c r="E41" s="30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" ht="33" customHeight="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" ht="18" customHeight="1">
       <c r="B42" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="37"/>
+        <v>51</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="39"/>
       <c r="E42" s="30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" ht="18" customHeight="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" ht="33" customHeight="1">
       <c r="B43" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="C43" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="37"/>
+        <v>54</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="D43" s="39"/>
       <c r="E43" s="30" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" ht="33" customHeight="1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" ht="18" customHeight="1">
       <c r="B44" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D44" s="37"/>
+        <v>57</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="39"/>
       <c r="E44" s="30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="2:5" ht="18" customHeight="1">
-      <c r="B45" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="37"/>
-      <c r="E45" s="30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" ht="18" customHeight="1">
-      <c r="B46" s="28" t="s">
+      <c r="B45" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="C45" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="D46" s="38"/>
-      <c r="E46" s="28"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="28"/>
+    </row>
+    <row r="47" spans="2:5" ht="20" customHeight="1">
+      <c r="B47" s="42" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
     </row>
     <row r="48" spans="2:5" ht="20" customHeight="1">
-      <c r="B48" s="39" t="s">
-        <v>3277</v>
-      </c>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-    </row>
-    <row r="49" spans="1:5" ht="20" customHeight="1">
-      <c r="B49" s="26" t="s">
+      <c r="B48" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C49" s="26" t="s">
+      <c r="C48" s="26" t="s">
         <v>21</v>
       </c>
+      <c r="D48" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="33"/>
+    </row>
+    <row r="49" spans="1:5" ht="18" customHeight="1">
+      <c r="B49" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>62</v>
+      </c>
       <c r="D49" s="40" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="E49" s="40"/>
     </row>
     <row r="50" spans="1:5" ht="18" customHeight="1">
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="C50" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E50" s="41"/>
-    </row>
-    <row r="51" spans="1:5" ht="18" customHeight="1">
+      <c r="C50" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E50" s="39"/>
+    </row>
+    <row r="51" spans="1:5" ht="33" customHeight="1">
       <c r="B51" s="30" t="s">
         <v>4</v>
       </c>
       <c r="C51" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D51" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" s="37"/>
-    </row>
-    <row r="52" spans="1:5" ht="33" customHeight="1">
+        <v>66</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="39"/>
+    </row>
+    <row r="52" spans="1:5" ht="18" customHeight="1">
       <c r="B52" s="30" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D52" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52" s="37"/>
+        <v>68</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E52" s="39"/>
     </row>
     <row r="53" spans="1:5" ht="18" customHeight="1">
       <c r="B53" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" s="39" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="39"/>
+    </row>
+    <row r="54" spans="1:5" ht="33" customHeight="1">
+      <c r="B54" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C53" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="D53" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="E53" s="37"/>
-    </row>
-    <row r="54" spans="1:5" ht="18" customHeight="1">
-      <c r="B54" s="30" t="s">
-        <v>8</v>
-      </c>
       <c r="C54" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="D54" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" s="37"/>
-    </row>
-    <row r="55" spans="1:5" ht="33" customHeight="1">
+        <v>72</v>
+      </c>
+      <c r="D54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="39"/>
+    </row>
+    <row r="55" spans="1:5" ht="18" customHeight="1">
       <c r="B55" s="30" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E55" s="37"/>
-    </row>
-    <row r="56" spans="1:5" ht="18" customHeight="1">
-      <c r="B56" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="D56" s="37" t="s">
+      <c r="D55" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="E56" s="37"/>
-    </row>
-    <row r="57" spans="1:5" ht="33" customHeight="1">
-      <c r="B57" s="28" t="s">
+      <c r="E55" s="39"/>
+    </row>
+    <row r="56" spans="1:5" ht="33" customHeight="1">
+      <c r="B56" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C56" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D57" s="38">
+      <c r="D56" s="41">
         <v>62</v>
       </c>
-      <c r="E57" s="38"/>
-    </row>
-    <row r="59" spans="1:5" ht="24" customHeight="1">
-      <c r="A59" s="34" t="s">
-        <v>3278</v>
-      </c>
-      <c r="B59" s="35"/>
-      <c r="C59" s="35"/>
-      <c r="D59" s="35"/>
-      <c r="E59" s="35"/>
-    </row>
-    <row r="60" spans="1:5" ht="34" customHeight="1">
-      <c r="A60" s="36" t="s">
-        <v>3279</v>
-      </c>
-      <c r="B60" s="36"/>
-      <c r="C60" s="36"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-    </row>
-    <row r="61" spans="1:5" ht="20" customHeight="1">
-      <c r="A61" s="26" t="s">
+      <c r="E56" s="41"/>
+    </row>
+    <row r="58" spans="1:5" ht="24" customHeight="1">
+      <c r="A58" s="37" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+    </row>
+    <row r="59" spans="1:5" ht="34" customHeight="1">
+      <c r="A59" s="36" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B59" s="36"/>
+      <c r="C59" s="36"/>
+      <c r="D59" s="36"/>
+      <c r="E59" s="36"/>
+    </row>
+    <row r="60" spans="1:5" ht="20" customHeight="1">
+      <c r="A60" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="B61" s="26" t="s">
+      <c r="B60" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C60" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="D61" s="26" t="s">
+      <c r="D60" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="E61" s="26" t="s">
-        <v>3280</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="78" customHeight="1">
-      <c r="A62" s="29" t="s">
-        <v>3281</v>
-      </c>
-      <c r="B62" s="27" t="s">
+      <c r="E60" s="26" t="s">
+        <v>3275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="78" customHeight="1">
+      <c r="A61" s="29" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B61" s="27" t="s">
         <v>3246</v>
       </c>
-      <c r="C62" s="27" t="s">
+      <c r="C61" s="27" t="s">
         <v>3247</v>
       </c>
-      <c r="D62" s="27" t="s">
+      <c r="D61" s="27" t="s">
         <v>3248</v>
       </c>
-      <c r="E62" s="27" t="s">
+      <c r="E61" s="27" t="s">
         <v>3249</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="93" hidden="1" customHeight="1">
-      <c r="A63" s="33" t="s">
-        <v>3266</v>
+    <row r="62" spans="1:5" ht="93" hidden="1" customHeight="1">
+      <c r="A62" s="32" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B62" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="108" hidden="1" customHeight="1">
+      <c r="A63" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B63" s="30" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C63" s="30" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D63" s="30" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E63" s="30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="108" hidden="1" customHeight="1">
-      <c r="A64" s="33" t="s">
-        <v>3266</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="63" hidden="1" customHeight="1">
+      <c r="A64" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B64" s="30" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C64" s="30" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D64" s="30" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E64" s="30" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A65" s="33" t="s">
-        <v>3266</v>
+    <row r="65" spans="1:5" ht="123" hidden="1" customHeight="1">
+      <c r="A65" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B65" s="30" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C65" s="30" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D65" s="30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E65" s="30" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="123" hidden="1" customHeight="1">
-      <c r="A66" s="33" t="s">
-        <v>3266</v>
+    <row r="66" spans="1:5" ht="303" hidden="1" customHeight="1">
+      <c r="A66" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B66" s="30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C66" s="30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D66" s="30" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E66" s="30" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" ht="303" hidden="1" customHeight="1">
-      <c r="A67" s="33" t="s">
-        <v>3266</v>
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="48" hidden="1" customHeight="1">
+      <c r="A67" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C67" s="30" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D67" s="30" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E67" s="30" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="48" hidden="1" customHeight="1">
-      <c r="A68" s="33" t="s">
-        <v>3266</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="63" hidden="1" customHeight="1">
+      <c r="A68" s="32" t="s">
+        <v>3261</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E68" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="63" hidden="1" customHeight="1">
-      <c r="A69" s="33" t="s">
-        <v>3266</v>
-      </c>
-      <c r="B69" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E69" s="30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="33" hidden="1" customHeight="1">
-      <c r="A70" s="32" t="s">
-        <v>3266</v>
-      </c>
-      <c r="B70" s="28" t="s">
+    <row r="69" spans="1:5" ht="33" hidden="1" customHeight="1">
+      <c r="A69" s="31" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B69" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="C70" s="28" t="s">
+      <c r="C69" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="D69" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="E70" s="28" t="s">
+      <c r="E69" s="28" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="D50:E50"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="D51:E51"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
@@ -13564,18 +13496,39 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="D48:E48"/>
     <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
